--- a/docs/data/jp/xlsx/4479.xlsx
+++ b/docs/data/jp/xlsx/4479.xlsx
@@ -6080,7 +6080,7 @@
     <row r="86">
       <c r="A86" s="20" t="inlineStr">
         <is>
-          <t>Lecture SFee Income NOI</t>
+          <t>강연료 등 수입</t>
         </is>
       </c>
       <c r="C86" s="22" t="n">
@@ -6148,7 +6148,7 @@
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>An Introduction Fee NOI</t>
+          <t>소개수수료</t>
         </is>
       </c>
       <c r="D88" s="22" t="n">
@@ -6229,7 +6229,7 @@
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>Point Return Income NOI</t>
+          <t>포인트 환원 수입</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
@@ -7524,7 +7524,7 @@
     <row r="120">
       <c r="A120" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Provision For Retirement Benefits Ope CF</t>
+          <t>퇴직급여충당금 증감액</t>
         </is>
       </c>
       <c r="C120" s="22" t="n">
@@ -7567,7 +7567,7 @@
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease Provision For Continuous Services Benefits Ope CF</t>
+          <t>근속 인센티브 충당금 증감액</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
@@ -8024,7 +8024,7 @@
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>Increase Decrease In Accrued Consumption Taxes Or Consumption Taxes Refund Receivable Ope CF</t>
+          <t>미지급·미수 소비세 증감액</t>
         </is>
       </c>
       <c r="C134" s="22" t="n">
@@ -11593,7 +11593,7 @@
     <row r="72">
       <c r="A72" s="20" t="inlineStr">
         <is>
-          <t>Cash Segregated As Deposits</t>
+          <t>프로젝트 예수용 예금</t>
         </is>
       </c>
       <c r="D72" s="22" t="n">
@@ -11618,7 +11618,7 @@
     <row r="73">
       <c r="A73" s="20" t="inlineStr">
         <is>
-          <t>Cash Segregated As Deposits CA</t>
+          <t>프로젝트 예수용 예금</t>
         </is>
       </c>
       <c r="C73" s="22" t="n">
@@ -12603,7 +12603,7 @@
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>Provision For Loss On Compensation CL</t>
+          <t>보상손실 충당금</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
@@ -12727,7 +12727,7 @@
     <row r="111">
       <c r="A111" s="20" t="inlineStr">
         <is>
-          <t>Provision For Continuous Services Benefits NCL</t>
+          <t>근속 인센티브 충당금</t>
         </is>
       </c>
       <c r="C111" s="22" t="n">

--- a/docs/data/jp/xlsx/4479.xlsx
+++ b/docs/data/jp/xlsx/4479.xlsx
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -323,6 +323,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -717,7 +720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AC158"/>
+  <dimension ref="A1:AC164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4249,10 +4252,12 @@
     <row r="47">
       <c r="A47" s="20" t="inlineStr">
         <is>
-          <t>현재 주가 ()</t>
-        </is>
-      </c>
-      <c r="B47" s="29" t="n"/>
+          <t>현재 주가 (2026.10.26)</t>
+        </is>
+      </c>
+      <c r="B47" s="29" t="n">
+        <v>932</v>
+      </c>
       <c r="C47" s="30" t="n"/>
       <c r="D47" s="31" t="n"/>
       <c r="E47" s="31" t="n"/>
@@ -4287,7 +4292,9 @@
           <t>발행주식수 (보통주)</t>
         </is>
       </c>
-      <c r="B48" s="29" t="n"/>
+      <c r="B48" s="29" t="n">
+        <v>12748700</v>
+      </c>
       <c r="C48" s="30" t="n"/>
       <c r="D48" s="31" t="n"/>
       <c r="E48" s="31" t="n"/>
@@ -5486,7 +5493,7 @@
     <row r="74">
       <c r="A74" s="43" t="inlineStr">
         <is>
-          <t>주가: 야후 파이낸스 일봉</t>
+          <t>주가: 야후 파이낸스 일봉 2026.10.26</t>
         </is>
       </c>
       <c r="C74" s="41" t="n"/>
@@ -5735,719 +5742,773 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="20" t="inlineStr">
+      <c r="A79" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G79" s="17">
+        <f>IF(OR(G78="",C78=""),"",IF(C78&lt;=0,"",IFERROR(G78/C78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H79" s="17">
+        <f>IF(OR(H78="",D78=""),"",IF(D78&lt;=0,"",IFERROR(H78/D78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I79" s="17">
+        <f>IF(OR(I78="",E78=""),"",IF(E78&lt;=0,"",IFERROR(I78/E78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J79" s="17">
+        <f>IF(OR(J78="",F78=""),"",IF(F78&lt;=0,"",IFERROR(J78/F78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K79" s="17">
+        <f>IF(OR(K78="",G78=""),"",IF(G78&lt;=0,"",IFERROR(K78/G78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L79" s="17">
+        <f>IF(OR(L78="",H78=""),"",IF(H78&lt;=0,"",IFERROR(L78/H78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M79" s="17">
+        <f>IF(OR(M78="",I78=""),"",IF(I78&lt;=0,"",IFERROR(M78/I78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N79" s="17">
+        <f>IF(OR(N78="",J78=""),"",IF(J78&lt;=0,"",IFERROR(N78/J78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U79" s="17">
+        <f>IF(OR(U78="",T78=""),"",IF(T78&lt;=0,"",IFERROR(U78/T78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V79" s="17">
+        <f>IF(OR(V78="",U78=""),"",IF(U78&lt;=0,"",IFERROR(V78/U78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W79" s="17">
+        <f>IF(OR(W78="",V78=""),"",IF(V78&lt;=0,"",IFERROR(W78/V78-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X79" s="17">
+        <f>IF(OR(X78="",W78=""),"",IF(W78&lt;=0,"",IFERROR(X78/W78-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="20" t="inlineStr">
         <is>
           <t>매출원가</t>
         </is>
       </c>
-      <c r="C79" s="22" t="n">
+      <c r="C80" s="22" t="n">
         <v>216.904</v>
       </c>
-      <c r="D79" s="22" t="n">
+      <c r="D80" s="22" t="n">
         <v>254.044</v>
       </c>
-      <c r="E79" s="22" t="n">
+      <c r="E80" s="22" t="n">
         <v>180.754</v>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F80" s="22" t="n">
         <v>204.504</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G80" s="22" t="n">
         <v>236.033</v>
       </c>
-      <c r="H79" s="22" t="n">
+      <c r="H80" s="22" t="n">
         <v>223.263</v>
       </c>
-      <c r="I79" s="22" t="n">
+      <c r="I80" s="22" t="n">
         <v>257.917</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J80" s="22" t="n">
         <v>338.887</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K80" s="22" t="n">
         <v>322.313</v>
       </c>
-      <c r="L79" s="22" t="n">
+      <c r="L80" s="22" t="n">
         <v>388.738</v>
       </c>
-      <c r="M79" s="22" t="n">
+      <c r="M80" s="22" t="n">
         <v>360.685</v>
       </c>
-      <c r="N79" s="22" t="n">
+      <c r="N80" s="22" t="n">
         <v>436.132</v>
       </c>
-      <c r="U79" s="22" t="n">
+      <c r="U80" s="22" t="n">
         <v>196.721</v>
       </c>
-      <c r="V79" s="22" t="n">
+      <c r="V80" s="22" t="n">
         <v>216.904</v>
       </c>
-      <c r="W79" s="22" t="n">
+      <c r="W80" s="22" t="n">
         <v>236.033</v>
       </c>
-      <c r="X79" s="22" t="n">
+      <c r="X80" s="22" t="n">
         <v>322.313</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="9" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="9" t="inlineStr">
         <is>
           <t>매출총이익</t>
         </is>
       </c>
-      <c r="C80" s="12" t="n">
+      <c r="C81" s="12" t="n">
         <v>813.5549999999999</v>
       </c>
-      <c r="D80" s="12" t="n">
+      <c r="D81" s="12" t="n">
         <v>775.851</v>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="E81" s="12" t="n">
         <v>649.415</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>667.182</v>
       </c>
-      <c r="G80" s="12" t="n">
+      <c r="G81" s="12" t="n">
         <v>685.024</v>
       </c>
-      <c r="H80" s="12" t="n">
+      <c r="H81" s="12" t="n">
         <v>757.45</v>
       </c>
-      <c r="I80" s="12" t="n">
+      <c r="I81" s="12" t="n">
         <v>812.115</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="J81" s="12" t="n">
         <v>959.7089999999999</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>906.343</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="L81" s="12" t="n">
         <v>1074.77</v>
       </c>
-      <c r="M80" s="12" t="n">
+      <c r="M81" s="12" t="n">
         <v>988.456</v>
       </c>
-      <c r="N80" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>1143.354</v>
       </c>
-      <c r="U80" s="12" t="n">
+      <c r="U81" s="12" t="n">
         <v>683.501</v>
       </c>
-      <c r="V80" s="12" t="n">
+      <c r="V81" s="12" t="n">
         <v>813.5549999999999</v>
       </c>
-      <c r="W80" s="12" t="n">
+      <c r="W81" s="12" t="n">
         <v>685.024</v>
       </c>
-      <c r="X80" s="12" t="n">
+      <c r="X81" s="12" t="n">
         <v>906.343</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="20" t="inlineStr">
-        <is>
-          <t>판매비와 관리비</t>
-        </is>
-      </c>
-      <c r="C81" s="22" t="n">
-        <v>842.942</v>
-      </c>
-      <c r="D81" s="22" t="n">
-        <v>792.751</v>
-      </c>
-      <c r="E81" s="22" t="n">
-        <v>731.366</v>
-      </c>
-      <c r="F81" s="22" t="n">
-        <v>682.4160000000001</v>
-      </c>
-      <c r="G81" s="22" t="n">
-        <v>633.579</v>
-      </c>
-      <c r="H81" s="22" t="n">
-        <v>656.987</v>
-      </c>
-      <c r="I81" s="22" t="n">
-        <v>650.847</v>
-      </c>
-      <c r="J81" s="22" t="n">
-        <v>801.341</v>
-      </c>
-      <c r="K81" s="22" t="n">
-        <v>879.178</v>
-      </c>
-      <c r="L81" s="22" t="n">
-        <v>740.644</v>
-      </c>
-      <c r="M81" s="22" t="n">
-        <v>754.188</v>
-      </c>
-      <c r="N81" s="22" t="n">
-        <v>867.3200000000001</v>
-      </c>
-      <c r="U81" s="22" t="n">
-        <v>918.429</v>
-      </c>
-      <c r="V81" s="22" t="n">
-        <v>842.942</v>
-      </c>
-      <c r="W81" s="22" t="n">
-        <v>633.579</v>
-      </c>
-      <c r="X81" s="22" t="n">
-        <v>879.178</v>
-      </c>
-    </row>
     <row r="82">
-      <c r="A82" s="9" t="inlineStr">
-        <is>
-          <t>영업이익</t>
-        </is>
-      </c>
-      <c r="C82" s="12" t="n">
-        <v>-29.388</v>
-      </c>
-      <c r="D82" s="12" t="n">
-        <v>-16.9</v>
-      </c>
-      <c r="E82" s="12" t="n">
-        <v>-81.95099999999999</v>
-      </c>
-      <c r="F82" s="12" t="n">
-        <v>-15.233</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>51.444</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>100.462</v>
-      </c>
-      <c r="I82" s="12" t="n">
-        <v>161.268</v>
-      </c>
-      <c r="J82" s="12" t="n">
-        <v>158.369</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>27.164</v>
-      </c>
-      <c r="L82" s="12" t="n">
-        <v>334.126</v>
-      </c>
-      <c r="M82" s="12" t="n">
-        <v>234.268</v>
-      </c>
-      <c r="N82" s="12" t="n">
-        <v>276.034</v>
-      </c>
-      <c r="U82" s="12" t="n">
-        <v>-234.928</v>
-      </c>
-      <c r="V82" s="12" t="n">
-        <v>-29.388</v>
-      </c>
-      <c r="W82" s="12" t="n">
-        <v>51.444</v>
-      </c>
-      <c r="X82" s="12" t="n">
-        <v>27.164</v>
+      <c r="A82" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G82" s="17">
+        <f>IF(OR(G81="",C81=""),"",IF(C81&lt;=0,"",IFERROR(G81/C81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H82" s="17">
+        <f>IF(OR(H81="",D81=""),"",IF(D81&lt;=0,"",IFERROR(H81/D81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I82" s="17">
+        <f>IF(OR(I81="",E81=""),"",IF(E81&lt;=0,"",IFERROR(I81/E81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J82" s="17">
+        <f>IF(OR(J81="",F81=""),"",IF(F81&lt;=0,"",IFERROR(J81/F81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K82" s="17">
+        <f>IF(OR(K81="",G81=""),"",IF(G81&lt;=0,"",IFERROR(K81/G81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L82" s="17">
+        <f>IF(OR(L81="",H81=""),"",IF(H81&lt;=0,"",IFERROR(L81/H81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M82" s="17">
+        <f>IF(OR(M81="",I81=""),"",IF(I81&lt;=0,"",IFERROR(M81/I81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N82" s="17">
+        <f>IF(OR(N81="",J81=""),"",IF(J81&lt;=0,"",IFERROR(N81/J81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U82" s="17">
+        <f>IF(OR(U81="",T81=""),"",IF(T81&lt;=0,"",IFERROR(U81/T81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V82" s="17">
+        <f>IF(OR(V81="",U81=""),"",IF(U81&lt;=0,"",IFERROR(V81/U81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W82" s="17">
+        <f>IF(OR(W81="",V81=""),"",IF(V81&lt;=0,"",IFERROR(W81/V81-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X82" s="17">
+        <f>IF(OR(X81="",W81=""),"",IF(W81&lt;=0,"",IFERROR(X81/W81-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="20" t="inlineStr">
         <is>
-          <t>이자수익</t>
+          <t>판매비와 관리비</t>
         </is>
       </c>
       <c r="C83" s="22" t="n">
-        <v>0.001</v>
+        <v>842.942</v>
       </c>
       <c r="D83" s="22" t="n">
-        <v>0.001</v>
+        <v>792.751</v>
       </c>
       <c r="E83" s="22" t="n">
-        <v>0.003</v>
+        <v>731.366</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>0.002</v>
+        <v>682.4160000000001</v>
       </c>
       <c r="G83" s="22" t="n">
-        <v>0.002</v>
+        <v>633.579</v>
       </c>
       <c r="H83" s="22" t="n">
-        <v>0.002</v>
+        <v>656.987</v>
       </c>
       <c r="I83" s="22" t="n">
-        <v>0.004</v>
+        <v>650.847</v>
       </c>
       <c r="J83" s="22" t="n">
-        <v>0.002</v>
+        <v>801.341</v>
       </c>
       <c r="K83" s="22" t="n">
-        <v>0.005</v>
+        <v>879.178</v>
       </c>
       <c r="L83" s="22" t="n">
-        <v>0.002</v>
+        <v>740.644</v>
       </c>
       <c r="M83" s="22" t="n">
-        <v>0.005</v>
+        <v>754.188</v>
       </c>
       <c r="N83" s="22" t="n">
-        <v>0.002</v>
+        <v>867.3200000000001</v>
       </c>
       <c r="U83" s="22" t="n">
-        <v>0</v>
+        <v>918.429</v>
       </c>
       <c r="V83" s="22" t="n">
-        <v>0.001</v>
+        <v>842.942</v>
       </c>
       <c r="W83" s="22" t="n">
-        <v>0.002</v>
+        <v>633.579</v>
       </c>
       <c r="X83" s="22" t="n">
-        <v>0.005</v>
+        <v>879.178</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="20" t="inlineStr">
-        <is>
-          <t>배당금수익</t>
-        </is>
-      </c>
-      <c r="C84" s="22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="D84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F84" s="22" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="G84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H84" s="22" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="I84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" s="22" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="K84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="22" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="M84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="U84" s="22" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="V84" s="22" t="n">
-        <v>0.007</v>
-      </c>
-      <c r="W84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="22" t="n">
-        <v>0</v>
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>영업이익</t>
+        </is>
+      </c>
+      <c r="C84" s="12" t="n">
+        <v>-29.388</v>
+      </c>
+      <c r="D84" s="12" t="n">
+        <v>-16.9</v>
+      </c>
+      <c r="E84" s="12" t="n">
+        <v>-81.95099999999999</v>
+      </c>
+      <c r="F84" s="12" t="n">
+        <v>-15.233</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>51.444</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>100.462</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>161.268</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>158.369</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>27.164</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>334.126</v>
+      </c>
+      <c r="M84" s="12" t="n">
+        <v>234.268</v>
+      </c>
+      <c r="N84" s="12" t="n">
+        <v>276.034</v>
+      </c>
+      <c r="U84" s="12" t="n">
+        <v>-234.928</v>
+      </c>
+      <c r="V84" s="12" t="n">
+        <v>-29.388</v>
+      </c>
+      <c r="W84" s="12" t="n">
+        <v>51.444</v>
+      </c>
+      <c r="X84" s="12" t="n">
+        <v>27.164</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="20" t="inlineStr">
-        <is>
-          <t>외환차익</t>
-        </is>
-      </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L85" s="22" t="n">
-        <v>0.1</v>
+      <c r="A85" s="45" t="inlineStr">
+        <is>
+          <t>OPM</t>
+        </is>
+      </c>
+      <c r="B85" s="3" t="inlineStr">
+        <is>
+          <t>영업이익 ÷ 매출</t>
+        </is>
+      </c>
+      <c r="C85" s="17">
+        <f>IF(OR(C84="",C78=""),"",IF(C78&lt;=0,"",IFERROR(C84/C78,"")))</f>
+        <v/>
+      </c>
+      <c r="D85" s="17">
+        <f>IF(OR(D84="",D78=""),"",IF(D78&lt;=0,"",IFERROR(D84/D78,"")))</f>
+        <v/>
+      </c>
+      <c r="E85" s="17">
+        <f>IF(OR(E84="",E78=""),"",IF(E78&lt;=0,"",IFERROR(E84/E78,"")))</f>
+        <v/>
+      </c>
+      <c r="F85" s="17">
+        <f>IF(OR(F84="",F78=""),"",IF(F78&lt;=0,"",IFERROR(F84/F78,"")))</f>
+        <v/>
+      </c>
+      <c r="G85" s="17">
+        <f>IF(OR(G84="",G78=""),"",IF(G78&lt;=0,"",IFERROR(G84/G78,"")))</f>
+        <v/>
+      </c>
+      <c r="H85" s="17">
+        <f>IF(OR(H84="",H78=""),"",IF(H78&lt;=0,"",IFERROR(H84/H78,"")))</f>
+        <v/>
+      </c>
+      <c r="I85" s="17">
+        <f>IF(OR(I84="",I78=""),"",IF(I78&lt;=0,"",IFERROR(I84/I78,"")))</f>
+        <v/>
+      </c>
+      <c r="J85" s="17">
+        <f>IF(OR(J84="",J78=""),"",IF(J78&lt;=0,"",IFERROR(J84/J78,"")))</f>
+        <v/>
+      </c>
+      <c r="K85" s="17">
+        <f>IF(OR(K84="",K78=""),"",IF(K78&lt;=0,"",IFERROR(K84/K78,"")))</f>
+        <v/>
+      </c>
+      <c r="L85" s="17">
+        <f>IF(OR(L84="",L78=""),"",IF(L78&lt;=0,"",IFERROR(L84/L78,"")))</f>
+        <v/>
+      </c>
+      <c r="M85" s="17">
+        <f>IF(OR(M84="",M78=""),"",IF(M78&lt;=0,"",IFERROR(M84/M78,"")))</f>
+        <v/>
+      </c>
+      <c r="N85" s="17">
+        <f>IF(OR(N84="",N78=""),"",IF(N78&lt;=0,"",IFERROR(N84/N78,"")))</f>
+        <v/>
+      </c>
+      <c r="U85" s="17">
+        <f>IF(OR(U84="",U78=""),"",IF(U78&lt;=0,"",IFERROR(U84/U78,"")))</f>
+        <v/>
+      </c>
+      <c r="V85" s="17">
+        <f>IF(OR(V84="",V78=""),"",IF(V78&lt;=0,"",IFERROR(V84/V78,"")))</f>
+        <v/>
+      </c>
+      <c r="W85" s="17">
+        <f>IF(OR(W84="",W78=""),"",IF(W78&lt;=0,"",IFERROR(W84/W78,"")))</f>
+        <v/>
+      </c>
+      <c r="X85" s="17">
+        <f>IF(OR(X84="",X78=""),"",IF(X78&lt;=0,"",IFERROR(X84/X78,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="20" t="inlineStr">
-        <is>
-          <t>강연료 등 수입</t>
-        </is>
-      </c>
-      <c r="C86" s="22" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="D86" s="22" t="n">
-        <v>1.968</v>
-      </c>
-      <c r="E86" s="22" t="n">
-        <v>1.472</v>
-      </c>
-      <c r="F86" s="22" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="G86" s="22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="H86" s="22" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I86" s="22" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J86" s="22" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K86" s="22" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="L86" s="22" t="n">
-        <v>0.098</v>
-      </c>
-      <c r="M86" s="22" t="n">
-        <v>0.141</v>
-      </c>
-      <c r="U86" s="22" t="n">
-        <v>2.089</v>
-      </c>
-      <c r="V86" s="22" t="n">
-        <v>1.617</v>
-      </c>
-      <c r="W86" s="22" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="X86" s="22" t="n">
-        <v>0.11</v>
+      <c r="A86" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G86" s="17">
+        <f>IF(OR(G84="",C84=""),"",IF(C84&lt;=0,"",IFERROR(G84/C84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H86" s="17">
+        <f>IF(OR(H84="",D84=""),"",IF(D84&lt;=0,"",IFERROR(H84/D84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I86" s="17">
+        <f>IF(OR(I84="",E84=""),"",IF(E84&lt;=0,"",IFERROR(I84/E84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J86" s="17">
+        <f>IF(OR(J84="",F84=""),"",IF(F84&lt;=0,"",IFERROR(J84/F84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K86" s="17">
+        <f>IF(OR(K84="",G84=""),"",IF(G84&lt;=0,"",IFERROR(K84/G84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L86" s="17">
+        <f>IF(OR(L84="",H84=""),"",IF(H84&lt;=0,"",IFERROR(L84/H84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M86" s="17">
+        <f>IF(OR(M84="",I84=""),"",IF(I84&lt;=0,"",IFERROR(M84/I84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N86" s="17">
+        <f>IF(OR(N84="",J84=""),"",IF(J84&lt;=0,"",IFERROR(N84/J84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U86" s="17">
+        <f>IF(OR(U84="",T84=""),"",IF(T84&lt;=0,"",IFERROR(U84/T84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V86" s="17">
+        <f>IF(OR(V84="",U84=""),"",IF(U84&lt;=0,"",IFERROR(V84/U84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W86" s="17">
+        <f>IF(OR(W84="",V84=""),"",IF(V84&lt;=0,"",IFERROR(W84/V84-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X86" s="17">
+        <f>IF(OR(X84="",W84=""),"",IF(W84&lt;=0,"",IFERROR(X84/W84-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="20" t="inlineStr">
         <is>
-          <t>고용조정 보조금</t>
-        </is>
+          <t>이자수익</t>
+        </is>
+      </c>
+      <c r="C87" s="22" t="n">
+        <v>0.001</v>
       </c>
       <c r="D87" s="22" t="n">
-        <v>0.388</v>
+        <v>0.001</v>
+      </c>
+      <c r="E87" s="22" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F87" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G87" s="22" t="n">
+        <v>0.002</v>
       </c>
       <c r="H87" s="22" t="n">
-        <v>0.406</v>
+        <v>0.002</v>
+      </c>
+      <c r="I87" s="22" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="J87" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="K87" s="22" t="n">
+        <v>0.005</v>
       </c>
       <c r="L87" s="22" t="n">
-        <v>0</v>
+        <v>0.002</v>
+      </c>
+      <c r="M87" s="22" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="N87" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="U87" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" s="22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="W87" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="X87" s="22" t="n">
+        <v>0.005</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="20" t="inlineStr">
         <is>
-          <t>소개수수료</t>
-        </is>
+          <t>배당금수익</t>
+        </is>
+      </c>
+      <c r="C88" s="22" t="n">
+        <v>0.007</v>
       </c>
       <c r="D88" s="22" t="n">
-        <v>0.196</v>
+        <v>0</v>
+      </c>
+      <c r="E88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F88" s="22" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G88" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="H88" s="22" t="n">
-        <v>0.197</v>
+        <v>0.013</v>
+      </c>
+      <c r="I88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="22" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="K88" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="L88" s="22" t="n">
+        <v>0.013</v>
+      </c>
+      <c r="M88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="22" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="U88" s="22" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="V88" s="22" t="n">
+        <v>0.007</v>
+      </c>
+      <c r="W88" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
-        </is>
-      </c>
-      <c r="C89" s="22" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="D89" s="22" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G89" s="22" t="n">
-        <v>0</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="H89" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="J89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="22" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V89" s="22" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="W89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X89" s="22" t="n">
-        <v>0</v>
+      <c r="L89" s="22" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="20" t="inlineStr">
         <is>
-          <t>보조금 수입</t>
+          <t>강연료 등 수입</t>
         </is>
       </c>
       <c r="C90" s="22" t="n">
-        <v>0</v>
+        <v>1.617</v>
+      </c>
+      <c r="D90" s="22" t="n">
+        <v>1.968</v>
+      </c>
+      <c r="E90" s="22" t="n">
+        <v>1.472</v>
+      </c>
+      <c r="F90" s="22" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="G90" s="22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H90" s="22" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I90" s="22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J90" s="22" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K90" s="22" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L90" s="22" t="n">
+        <v>0.098</v>
+      </c>
+      <c r="M90" s="22" t="n">
+        <v>0.141</v>
       </c>
       <c r="U90" s="22" t="n">
-        <v>0</v>
+        <v>2.089</v>
       </c>
       <c r="V90" s="22" t="n">
-        <v>0</v>
+        <v>1.617</v>
+      </c>
+      <c r="W90" s="22" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="X90" s="22" t="n">
+        <v>0.11</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="20" t="inlineStr">
         <is>
-          <t>포인트 환원 수입</t>
+          <t>고용조정 보조금</t>
         </is>
       </c>
       <c r="D91" s="22" t="n">
-        <v>0</v>
+        <v>0.388</v>
       </c>
       <c r="H91" s="22" t="n">
-        <v>0.206</v>
-      </c>
-      <c r="I91" s="22" t="n">
-        <v>0.236</v>
+        <v>0.406</v>
       </c>
       <c r="L91" s="22" t="n">
-        <v>0.221</v>
-      </c>
-      <c r="M91" s="22" t="n">
-        <v>0.211</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="C92" s="22" t="n">
-        <v>0.569</v>
+          <t>소개수수료</t>
+        </is>
       </c>
       <c r="D92" s="22" t="n">
-        <v>0.002</v>
-      </c>
-      <c r="E92" s="22" t="n">
-        <v>0.707</v>
-      </c>
-      <c r="F92" s="22" t="n">
-        <v>0.114</v>
-      </c>
-      <c r="G92" s="22" t="n">
-        <v>0.045</v>
+        <v>0.196</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="I92" s="22" t="n">
-        <v>0.745</v>
-      </c>
-      <c r="J92" s="22" t="n">
-        <v>2.504</v>
-      </c>
-      <c r="K92" s="22" t="n">
-        <v>-0.229</v>
+        <v>0.197</v>
       </c>
       <c r="L92" s="22" t="n">
-        <v>0.026</v>
-      </c>
-      <c r="M92" s="22" t="n">
-        <v>0.122</v>
-      </c>
-      <c r="N92" s="22" t="n">
-        <v>1.114</v>
-      </c>
-      <c r="U92" s="22" t="n">
-        <v>-0.096</v>
-      </c>
-      <c r="V92" s="22" t="n">
-        <v>0.569</v>
-      </c>
-      <c r="W92" s="22" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="X92" s="22" t="n">
-        <v>-0.229</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="20" t="inlineStr">
         <is>
-          <t>영업외수익 합계</t>
+          <t>보조금 수입</t>
         </is>
       </c>
       <c r="C93" s="22" t="n">
-        <v>2.535</v>
+        <v>0.34</v>
       </c>
       <c r="D93" s="22" t="n">
-        <v>2.897</v>
+        <v>0.34</v>
       </c>
       <c r="E93" s="22" t="n">
-        <v>1.596</v>
+        <v>0</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>0.882</v>
+        <v>0</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>0.925</v>
+        <v>0</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>1.572</v>
+        <v>1</v>
       </c>
       <c r="J93" s="22" t="n">
-        <v>1.807</v>
+        <v>0</v>
       </c>
       <c r="K93" s="22" t="n">
-        <v>24.235</v>
-      </c>
-      <c r="L93" s="22" t="n">
-        <v>0.463</v>
-      </c>
-      <c r="M93" s="22" t="n">
-        <v>0.379</v>
+        <v>0</v>
       </c>
       <c r="N93" s="22" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="U93" s="22" t="n">
-        <v>1.995</v>
+        <v>0</v>
       </c>
       <c r="V93" s="22" t="n">
-        <v>2.535</v>
+        <v>0.34</v>
       </c>
       <c r="W93" s="22" t="n">
-        <v>0.882</v>
+        <v>0</v>
       </c>
       <c r="X93" s="22" t="n">
-        <v>24.235</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="20" t="inlineStr">
         <is>
-          <t>외환차손</t>
-        </is>
-      </c>
-      <c r="D94" s="22" t="n">
-        <v>0.172</v>
-      </c>
-      <c r="E94" s="22" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="F94" s="22" t="n">
-        <v>-0.267</v>
-      </c>
-      <c r="G94" s="22" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="H94" s="22" t="n">
-        <v>0.521</v>
-      </c>
-      <c r="I94" s="22" t="n">
-        <v>0.721</v>
-      </c>
-      <c r="J94" s="22" t="n">
-        <v>-0.761</v>
-      </c>
-      <c r="K94" s="22" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="L94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M94" s="22" t="n">
-        <v>0.276</v>
-      </c>
-      <c r="N94" s="22" t="n">
-        <v>0.229</v>
-      </c>
-      <c r="W94" s="22" t="n">
-        <v>1.566</v>
-      </c>
-      <c r="X94" s="22" t="n">
-        <v>0.024</v>
+          <t>보조금 수입</t>
+        </is>
+      </c>
+      <c r="C94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U94" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V94" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="20" t="inlineStr">
         <is>
-          <t>주식교부비 상각</t>
-        </is>
-      </c>
-      <c r="C95" s="22" t="n">
-        <v>1.47</v>
+          <t>포인트 환원 수입</t>
+        </is>
       </c>
       <c r="D95" s="22" t="n">
-        <v>1.443</v>
-      </c>
-      <c r="E95" s="22" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="F95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G95" s="22" t="n">
         <v>0</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>0</v>
+        <v>0.206</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U95" s="22" t="n">
-        <v>2.878</v>
-      </c>
-      <c r="V95" s="22" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="W95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X95" s="22" t="n">
-        <v>0</v>
+        <v>0.236</v>
+      </c>
+      <c r="L95" s="22" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="M95" s="22" t="n">
+        <v>0.211</v>
       </c>
     </row>
     <row r="96">
@@ -6457,163 +6518,193 @@
         </is>
       </c>
       <c r="C96" s="22" t="n">
-        <v>-0.18</v>
+        <v>0.569</v>
+      </c>
+      <c r="D96" s="22" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="E96" s="22" t="n">
+        <v>0.707</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>0</v>
+        <v>0.114</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>0</v>
+        <v>0.045</v>
+      </c>
+      <c r="H96" s="22" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="I96" s="22" t="n">
+        <v>0.745</v>
       </c>
       <c r="J96" s="22" t="n">
-        <v>0</v>
+        <v>2.504</v>
       </c>
       <c r="K96" s="22" t="n">
-        <v>-0.1</v>
+        <v>-0.229</v>
+      </c>
+      <c r="L96" s="22" t="n">
+        <v>0.026</v>
+      </c>
+      <c r="M96" s="22" t="n">
+        <v>0.122</v>
       </c>
       <c r="N96" s="22" t="n">
-        <v>0</v>
+        <v>1.114</v>
       </c>
       <c r="U96" s="22" t="n">
-        <v>0.051</v>
+        <v>-0.096</v>
       </c>
       <c r="V96" s="22" t="n">
-        <v>-0.18</v>
+        <v>0.569</v>
       </c>
       <c r="W96" s="22" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="X96" s="22" t="n">
-        <v>-0.1</v>
+        <v>-0.229</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="20" t="inlineStr">
         <is>
-          <t>영업외비용 합계</t>
+          <t>영업외수익 합계</t>
         </is>
       </c>
       <c r="C97" s="22" t="n">
-        <v>1.29</v>
+        <v>2.535</v>
       </c>
       <c r="D97" s="22" t="n">
-        <v>1.616</v>
+        <v>2.897</v>
       </c>
       <c r="E97" s="22" t="n">
-        <v>0.596</v>
+        <v>1.596</v>
       </c>
       <c r="F97" s="22" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="G97" s="22" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="H97" s="22" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="I97" s="22" t="n">
+        <v>1.572</v>
+      </c>
+      <c r="J97" s="22" t="n">
+        <v>1.807</v>
+      </c>
+      <c r="K97" s="22" t="n">
+        <v>24.235</v>
+      </c>
+      <c r="L97" s="22" t="n">
+        <v>0.463</v>
+      </c>
+      <c r="M97" s="22" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="N97" s="22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="U97" s="22" t="n">
+        <v>1.995</v>
+      </c>
+      <c r="V97" s="22" t="n">
+        <v>2.535</v>
+      </c>
+      <c r="W97" s="22" t="n">
+        <v>0.882</v>
+      </c>
+      <c r="X97" s="22" t="n">
+        <v>24.235</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="20" t="inlineStr">
+        <is>
+          <t>외환차손</t>
+        </is>
+      </c>
+      <c r="D98" s="22" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="E98" s="22" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="F98" s="22" t="n">
         <v>-0.267</v>
       </c>
-      <c r="G97" s="22" t="n">
+      <c r="G98" s="22" t="n">
         <v>1.566</v>
       </c>
-      <c r="H97" s="22" t="n">
+      <c r="H98" s="22" t="n">
         <v>0.521</v>
       </c>
-      <c r="I97" s="22" t="n">
-        <v>0.821</v>
-      </c>
-      <c r="J97" s="22" t="n">
+      <c r="I98" s="22" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="J98" s="22" t="n">
         <v>-0.761</v>
       </c>
-      <c r="K97" s="22" t="n">
-        <v>-0.076</v>
-      </c>
-      <c r="L97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="22" t="n">
+      <c r="K98" s="22" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="L98" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="22" t="n">
         <v>0.276</v>
       </c>
-      <c r="N97" s="22" t="n">
-        <v>0.288</v>
-      </c>
-      <c r="U97" s="22" t="n">
-        <v>2.929</v>
-      </c>
-      <c r="V97" s="22" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W97" s="22" t="n">
+      <c r="N98" s="22" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="W98" s="22" t="n">
         <v>1.566</v>
       </c>
-      <c r="X97" s="22" t="n">
-        <v>-0.076</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="9" t="inlineStr">
-        <is>
-          <t>경상이익</t>
-        </is>
-      </c>
-      <c r="C98" s="12" t="n">
-        <v>-28.143</v>
-      </c>
-      <c r="D98" s="12" t="n">
-        <v>-15.619</v>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>-80.95</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>-14.414</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>100.866</v>
-      </c>
-      <c r="I98" s="12" t="n">
-        <v>162.019</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>160.938</v>
-      </c>
-      <c r="K98" s="12" t="n">
-        <v>51.474</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>334.589</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>234.372</v>
-      </c>
-      <c r="N98" s="12" t="n">
-        <v>279.494</v>
-      </c>
-      <c r="U98" s="12" t="n">
-        <v>-235.862</v>
-      </c>
-      <c r="V98" s="12" t="n">
-        <v>-28.143</v>
-      </c>
-      <c r="W98" s="12" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="X98" s="12" t="n">
-        <v>51.474</v>
+      <c r="X98" s="22" t="n">
+        <v>0.024</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각이익</t>
+          <t>주식교부비 상각</t>
         </is>
       </c>
       <c r="C99" s="22" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="D99" s="22" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="E99" s="22" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="F99" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G99" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="H99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="K99" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="U99" s="22" t="n">
+        <v>2.878</v>
+      </c>
       <c r="V99" s="22" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W99" s="22" t="n">
         <v>0</v>
@@ -6625,2279 +6716,2571 @@
     <row r="100">
       <c r="A100" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각이익</t>
+          <t>기타</t>
         </is>
       </c>
       <c r="C100" s="22" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="F100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="N100" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U100" s="22" t="n">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="V100" s="22" t="n">
-        <v>0</v>
+        <v>-0.18</v>
+      </c>
+      <c r="W100" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X100" s="22" t="n">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
+          <t>영업외비용 합계</t>
         </is>
       </c>
       <c r="C101" s="22" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="D101" s="22" t="n">
-        <v>0</v>
+        <v>1.616</v>
       </c>
       <c r="E101" s="22" t="n">
-        <v>3.1</v>
+        <v>0.596</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>3.1</v>
+        <v>-0.267</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>0</v>
+        <v>1.566</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>7.75</v>
+        <v>0.521</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>2.015</v>
+        <v>0.821</v>
       </c>
       <c r="J101" s="22" t="n">
-        <v>0</v>
+        <v>-0.761</v>
       </c>
       <c r="K101" s="22" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
       <c r="L101" s="22" t="n">
         <v>0</v>
       </c>
       <c r="M101" s="22" t="n">
-        <v>0</v>
+        <v>0.276</v>
       </c>
       <c r="N101" s="22" t="n">
-        <v>0</v>
+        <v>0.288</v>
+      </c>
+      <c r="U101" s="22" t="n">
+        <v>2.929</v>
       </c>
       <c r="V101" s="22" t="n">
-        <v>3.1</v>
+        <v>1.29</v>
       </c>
       <c r="W101" s="22" t="n">
-        <v>0</v>
+        <v>1.566</v>
       </c>
       <c r="X101" s="22" t="n">
-        <v>0</v>
+        <v>-0.076</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="20" t="inlineStr">
-        <is>
-          <t>특별이익 합계</t>
-        </is>
-      </c>
-      <c r="C102" s="22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="D102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" s="22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="F102" s="22" t="n">
-        <v>3.211</v>
-      </c>
-      <c r="G102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="22" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="I102" s="22" t="n">
-        <v>2.015</v>
-      </c>
-      <c r="J102" s="22" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="K102" s="22" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V102" s="22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="W102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X102" s="22" t="n">
-        <v>0.03</v>
+      <c r="A102" s="9" t="inlineStr">
+        <is>
+          <t>경상이익</t>
+        </is>
+      </c>
+      <c r="C102" s="12" t="n">
+        <v>-28.143</v>
+      </c>
+      <c r="D102" s="12" t="n">
+        <v>-15.619</v>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>-80.95</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>-14.414</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>100.866</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>162.019</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>160.938</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>51.474</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>334.589</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>234.372</v>
+      </c>
+      <c r="N102" s="12" t="n">
+        <v>279.494</v>
+      </c>
+      <c r="U102" s="12" t="n">
+        <v>-235.862</v>
+      </c>
+      <c r="V102" s="12" t="n">
+        <v>-28.143</v>
+      </c>
+      <c r="W102" s="12" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="X102" s="12" t="n">
+        <v>51.474</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="G103" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="22" t="n">
-        <v>4.149</v>
-      </c>
-      <c r="K103" s="22" t="n">
-        <v>14.458</v>
-      </c>
-      <c r="N103" s="22" t="n">
-        <v>30.298</v>
-      </c>
-      <c r="W103" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X103" s="22" t="n">
-        <v>14.458</v>
+      <c r="A103" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G103" s="17">
+        <f>IF(OR(G102="",C102=""),"",IF(C102&lt;=0,"",IFERROR(G102/C102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H103" s="17">
+        <f>IF(OR(H102="",D102=""),"",IF(D102&lt;=0,"",IFERROR(H102/D102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I103" s="17">
+        <f>IF(OR(I102="",E102=""),"",IF(E102&lt;=0,"",IFERROR(I102/E102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J103" s="17">
+        <f>IF(OR(J102="",F102=""),"",IF(F102&lt;=0,"",IFERROR(J102/F102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K103" s="17">
+        <f>IF(OR(K102="",G102=""),"",IF(G102&lt;=0,"",IFERROR(K102/G102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L103" s="17">
+        <f>IF(OR(L102="",H102=""),"",IF(H102&lt;=0,"",IFERROR(L102/H102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M103" s="17">
+        <f>IF(OR(M102="",I102=""),"",IF(I102&lt;=0,"",IFERROR(M102/I102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N103" s="17">
+        <f>IF(OR(N102="",J102=""),"",IF(J102&lt;=0,"",IFERROR(N102/J102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U103" s="17">
+        <f>IF(OR(U102="",T102=""),"",IF(T102&lt;=0,"",IFERROR(U102/T102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V103" s="17">
+        <f>IF(OR(V102="",U102=""),"",IF(U102&lt;=0,"",IFERROR(V102/U102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W103" s="17">
+        <f>IF(OR(W102="",V102=""),"",IF(V102&lt;=0,"",IFERROR(W102/V102-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X103" s="17">
+        <f>IF(OR(X102="",W102=""),"",IF(W102&lt;=0,"",IFERROR(X102/W102-1,"")))</f>
+        <v/>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손실</t>
+          <t>고정자산 매각이익</t>
         </is>
       </c>
       <c r="C104" s="22" t="n">
-        <v>24.397</v>
+        <v>0</v>
       </c>
       <c r="G104" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="22" t="n">
-        <v>35.744</v>
+        <v>0</v>
       </c>
       <c r="V104" s="22" t="n">
-        <v>24.397</v>
+        <v>0</v>
       </c>
       <c r="W104" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X104" s="22" t="n">
-        <v>35.744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="20" t="inlineStr">
         <is>
-          <t>특별손실 합계</t>
+          <t>투자유가증권 매각이익</t>
         </is>
       </c>
       <c r="C105" s="22" t="n">
-        <v>24.397</v>
-      </c>
-      <c r="G105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="22" t="n">
-        <v>4.149</v>
-      </c>
-      <c r="K105" s="22" t="n">
-        <v>55.805</v>
-      </c>
-      <c r="N105" s="22" t="n">
-        <v>30.298</v>
+        <v>0</v>
+      </c>
+      <c r="U105" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V105" s="22" t="n">
-        <v>24.397</v>
-      </c>
-      <c r="W105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X105" s="22" t="n">
-        <v>55.805</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="9" t="inlineStr">
-        <is>
-          <t>법인세차감전 순이익</t>
-        </is>
-      </c>
-      <c r="C106" s="12" t="n">
-        <v>-49.44</v>
-      </c>
-      <c r="D106" s="12" t="n">
-        <v>-15.619</v>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>-77.84999999999999</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>-89.443</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>108.616</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>164.034</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>156.796</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>334.589</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>213.879</v>
-      </c>
-      <c r="N106" s="12" t="n">
-        <v>249.197</v>
-      </c>
-      <c r="U106" s="12" t="n">
-        <v>-1294.937</v>
-      </c>
-      <c r="V106" s="12" t="n">
-        <v>-49.44</v>
-      </c>
-      <c r="W106" s="12" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="X106" s="12" t="n">
-        <v>-4.3</v>
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>신주예약권 환입이익</t>
+        </is>
+      </c>
+      <c r="C106" s="22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" s="22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="F106" s="22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="G106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="22" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="I106" s="22" t="n">
+        <v>2.015</v>
+      </c>
+      <c r="J106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V106" s="22" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="W106" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X106" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="20" t="inlineStr">
         <is>
-          <t>법인세·주민세·사업세</t>
+          <t>특별이익 합계</t>
         </is>
       </c>
       <c r="C107" s="22" t="n">
-        <v>2.821</v>
+        <v>3.1</v>
       </c>
       <c r="D107" s="22" t="n">
-        <v>2.759</v>
+        <v>0</v>
       </c>
       <c r="E107" s="22" t="n">
-        <v>2.765</v>
+        <v>3.1</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>2.763</v>
+        <v>3.211</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>2.926</v>
+        <v>0</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>8.222</v>
+        <v>7.75</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>12.442</v>
+        <v>2.015</v>
       </c>
       <c r="J107" s="22" t="n">
-        <v>26.437</v>
+        <v>0.008</v>
       </c>
       <c r="K107" s="22" t="n">
-        <v>2.942</v>
+        <v>0.03</v>
       </c>
       <c r="L107" s="22" t="n">
-        <v>29.27</v>
+        <v>0</v>
       </c>
       <c r="M107" s="22" t="n">
-        <v>35.657</v>
+        <v>0</v>
       </c>
       <c r="N107" s="22" t="n">
-        <v>41.893</v>
+        <v>0</v>
       </c>
       <c r="U107" s="22" t="n">
-        <v>-15.616</v>
+        <v>0</v>
       </c>
       <c r="V107" s="22" t="n">
-        <v>2.821</v>
+        <v>3.1</v>
       </c>
       <c r="W107" s="22" t="n">
-        <v>2.926</v>
+        <v>0</v>
       </c>
       <c r="X107" s="22" t="n">
-        <v>2.942</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="20" t="inlineStr">
         <is>
-          <t>법인세 조정액</t>
-        </is>
-      </c>
-      <c r="C108" s="22" t="n">
-        <v>-23.754</v>
-      </c>
-      <c r="D108" s="22" t="n">
-        <v>-12.318</v>
-      </c>
-      <c r="E108" s="22" t="n">
-        <v>-9.74</v>
-      </c>
-      <c r="F108" s="22" t="n">
-        <v>-7.035</v>
+          <t>손상차손</t>
+        </is>
       </c>
       <c r="G108" s="22" t="n">
-        <v>-10.67</v>
-      </c>
-      <c r="H108" s="22" t="n">
-        <v>-3.714</v>
-      </c>
-      <c r="I108" s="22" t="n">
-        <v>7.957</v>
+        <v>0</v>
       </c>
       <c r="J108" s="22" t="n">
-        <v>-7.555</v>
+        <v>4.149</v>
       </c>
       <c r="K108" s="22" t="n">
-        <v>-28.841</v>
-      </c>
-      <c r="L108" s="22" t="n">
-        <v>15.196</v>
-      </c>
-      <c r="M108" s="22" t="n">
-        <v>-15.643</v>
+        <v>14.458</v>
       </c>
       <c r="N108" s="22" t="n">
-        <v>7.509</v>
-      </c>
-      <c r="U108" s="22" t="n">
-        <v>75.036</v>
-      </c>
-      <c r="V108" s="22" t="n">
-        <v>-23.754</v>
+        <v>30.298</v>
       </c>
       <c r="W108" s="22" t="n">
-        <v>-10.67</v>
+        <v>0</v>
       </c>
       <c r="X108" s="22" t="n">
-        <v>-28.841</v>
+        <v>14.458</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="20" t="inlineStr">
         <is>
+          <t>투자유가증권 평가손실</t>
+        </is>
+      </c>
+      <c r="C109" s="22" t="n">
+        <v>24.397</v>
+      </c>
+      <c r="G109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="22" t="n">
+        <v>35.744</v>
+      </c>
+      <c r="V109" s="22" t="n">
+        <v>24.397</v>
+      </c>
+      <c r="W109" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X109" s="22" t="n">
+        <v>35.744</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="20" t="inlineStr">
+        <is>
+          <t>특별손실 합계</t>
+        </is>
+      </c>
+      <c r="C110" s="22" t="n">
+        <v>24.397</v>
+      </c>
+      <c r="G110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="22" t="n">
+        <v>4.149</v>
+      </c>
+      <c r="K110" s="22" t="n">
+        <v>55.805</v>
+      </c>
+      <c r="N110" s="22" t="n">
+        <v>30.298</v>
+      </c>
+      <c r="V110" s="22" t="n">
+        <v>24.397</v>
+      </c>
+      <c r="W110" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X110" s="22" t="n">
+        <v>55.805</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="9" t="inlineStr">
+        <is>
+          <t>법인세차감전 순이익</t>
+        </is>
+      </c>
+      <c r="C111" s="12" t="n">
+        <v>-49.44</v>
+      </c>
+      <c r="D111" s="12" t="n">
+        <v>-15.619</v>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>-77.84999999999999</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>-89.443</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>108.616</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>164.034</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>156.796</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>334.589</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>213.879</v>
+      </c>
+      <c r="N111" s="12" t="n">
+        <v>249.197</v>
+      </c>
+      <c r="U111" s="12" t="n">
+        <v>-1294.937</v>
+      </c>
+      <c r="V111" s="12" t="n">
+        <v>-49.44</v>
+      </c>
+      <c r="W111" s="12" t="n">
+        <v>50.76</v>
+      </c>
+      <c r="X111" s="12" t="n">
+        <v>-4.3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="20" t="inlineStr">
+        <is>
+          <t>법인세·주민세·사업세</t>
+        </is>
+      </c>
+      <c r="C112" s="22" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="D112" s="22" t="n">
+        <v>2.759</v>
+      </c>
+      <c r="E112" s="22" t="n">
+        <v>2.765</v>
+      </c>
+      <c r="F112" s="22" t="n">
+        <v>2.763</v>
+      </c>
+      <c r="G112" s="22" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="H112" s="22" t="n">
+        <v>8.222</v>
+      </c>
+      <c r="I112" s="22" t="n">
+        <v>12.442</v>
+      </c>
+      <c r="J112" s="22" t="n">
+        <v>26.437</v>
+      </c>
+      <c r="K112" s="22" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="L112" s="22" t="n">
+        <v>29.27</v>
+      </c>
+      <c r="M112" s="22" t="n">
+        <v>35.657</v>
+      </c>
+      <c r="N112" s="22" t="n">
+        <v>41.893</v>
+      </c>
+      <c r="U112" s="22" t="n">
+        <v>-15.616</v>
+      </c>
+      <c r="V112" s="22" t="n">
+        <v>2.821</v>
+      </c>
+      <c r="W112" s="22" t="n">
+        <v>2.926</v>
+      </c>
+      <c r="X112" s="22" t="n">
+        <v>2.942</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="20" t="inlineStr">
+        <is>
+          <t>법인세 조정액</t>
+        </is>
+      </c>
+      <c r="C113" s="22" t="n">
+        <v>-23.754</v>
+      </c>
+      <c r="D113" s="22" t="n">
+        <v>-12.318</v>
+      </c>
+      <c r="E113" s="22" t="n">
+        <v>-9.74</v>
+      </c>
+      <c r="F113" s="22" t="n">
+        <v>-7.035</v>
+      </c>
+      <c r="G113" s="22" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="H113" s="22" t="n">
+        <v>-3.714</v>
+      </c>
+      <c r="I113" s="22" t="n">
+        <v>7.957</v>
+      </c>
+      <c r="J113" s="22" t="n">
+        <v>-7.555</v>
+      </c>
+      <c r="K113" s="22" t="n">
+        <v>-28.841</v>
+      </c>
+      <c r="L113" s="22" t="n">
+        <v>15.196</v>
+      </c>
+      <c r="M113" s="22" t="n">
+        <v>-15.643</v>
+      </c>
+      <c r="N113" s="22" t="n">
+        <v>7.509</v>
+      </c>
+      <c r="U113" s="22" t="n">
+        <v>75.036</v>
+      </c>
+      <c r="V113" s="22" t="n">
+        <v>-23.754</v>
+      </c>
+      <c r="W113" s="22" t="n">
+        <v>-10.67</v>
+      </c>
+      <c r="X113" s="22" t="n">
+        <v>-28.841</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="20" t="inlineStr">
+        <is>
           <t>법인세 등 합계</t>
         </is>
       </c>
-      <c r="C109" s="22" t="n">
+      <c r="C114" s="22" t="n">
         <v>-20.932</v>
       </c>
-      <c r="D109" s="22" t="n">
+      <c r="D114" s="22" t="n">
         <v>-9.558</v>
       </c>
-      <c r="E109" s="22" t="n">
+      <c r="E114" s="22" t="n">
         <v>-6.976</v>
       </c>
-      <c r="F109" s="22" t="n">
+      <c r="F114" s="22" t="n">
         <v>-4.272</v>
       </c>
-      <c r="G109" s="22" t="n">
+      <c r="G114" s="22" t="n">
         <v>-7.743</v>
       </c>
-      <c r="H109" s="22" t="n">
+      <c r="H114" s="22" t="n">
         <v>4.507</v>
       </c>
-      <c r="I109" s="22" t="n">
+      <c r="I114" s="22" t="n">
         <v>20.4</v>
       </c>
-      <c r="J109" s="22" t="n">
+      <c r="J114" s="22" t="n">
         <v>18.882</v>
       </c>
-      <c r="K109" s="22" t="n">
+      <c r="K114" s="22" t="n">
         <v>-25.899</v>
       </c>
-      <c r="L109" s="22" t="n">
+      <c r="L114" s="22" t="n">
         <v>44.467</v>
       </c>
-      <c r="M109" s="22" t="n">
+      <c r="M114" s="22" t="n">
         <v>20.012</v>
       </c>
-      <c r="N109" s="22" t="n">
+      <c r="N114" s="22" t="n">
         <v>49.404</v>
       </c>
-      <c r="U109" s="22" t="n">
+      <c r="U114" s="22" t="n">
         <v>59.422</v>
       </c>
-      <c r="V109" s="22" t="n">
+      <c r="V114" s="22" t="n">
         <v>-20.932</v>
       </c>
-      <c r="W109" s="22" t="n">
+      <c r="W114" s="22" t="n">
         <v>-7.743</v>
       </c>
-      <c r="X109" s="22" t="n">
+      <c r="X114" s="22" t="n">
         <v>-25.899</v>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="9" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="9" t="inlineStr">
         <is>
           <t>순이익</t>
         </is>
       </c>
-      <c r="C110" s="12" t="n">
+      <c r="C115" s="12" t="n">
         <v>-28.507</v>
       </c>
-      <c r="D110" s="12" t="n">
+      <c r="D115" s="12" t="n">
         <v>-6.06</v>
       </c>
-      <c r="E110" s="12" t="n">
+      <c r="E115" s="12" t="n">
         <v>-70.875</v>
       </c>
-      <c r="F110" s="12" t="n">
+      <c r="F115" s="12" t="n">
         <v>-85.17100000000001</v>
       </c>
-      <c r="G110" s="12" t="n">
+      <c r="G115" s="12" t="n">
         <v>58.503</v>
       </c>
-      <c r="H110" s="12" t="n">
+      <c r="H115" s="12" t="n">
         <v>104.108</v>
       </c>
-      <c r="I110" s="12" t="n">
+      <c r="I115" s="12" t="n">
         <v>143.634</v>
       </c>
-      <c r="J110" s="12" t="n">
+      <c r="J115" s="12" t="n">
         <v>137.915</v>
       </c>
-      <c r="K110" s="12" t="n">
+      <c r="K115" s="12" t="n">
         <v>21.599</v>
       </c>
-      <c r="L110" s="12" t="n">
+      <c r="L115" s="12" t="n">
         <v>290.121</v>
       </c>
-      <c r="M110" s="12" t="n">
+      <c r="M115" s="12" t="n">
         <v>193.867</v>
       </c>
-      <c r="N110" s="12" t="n">
+      <c r="N115" s="12" t="n">
         <v>199.793</v>
       </c>
-      <c r="U110" s="12" t="n">
+      <c r="U115" s="12" t="n">
         <v>-1354.36</v>
       </c>
-      <c r="V110" s="12" t="n">
+      <c r="V115" s="12" t="n">
         <v>-28.507</v>
       </c>
-      <c r="W110" s="12" t="n">
+      <c r="W115" s="12" t="n">
         <v>58.503</v>
       </c>
-      <c r="X110" s="12" t="n">
+      <c r="X115" s="12" t="n">
         <v>21.599</v>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="18" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="45" t="inlineStr">
+        <is>
+          <t>YoY</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>전년 같은 분기·전년 대비</t>
+        </is>
+      </c>
+      <c r="G116" s="17">
+        <f>IF(OR(G115="",C115=""),"",IF(C115&lt;=0,"",IFERROR(G115/C115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="H116" s="17">
+        <f>IF(OR(H115="",D115=""),"",IF(D115&lt;=0,"",IFERROR(H115/D115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="I116" s="17">
+        <f>IF(OR(I115="",E115=""),"",IF(E115&lt;=0,"",IFERROR(I115/E115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="J116" s="17">
+        <f>IF(OR(J115="",F115=""),"",IF(F115&lt;=0,"",IFERROR(J115/F115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="K116" s="17">
+        <f>IF(OR(K115="",G115=""),"",IF(G115&lt;=0,"",IFERROR(K115/G115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="L116" s="17">
+        <f>IF(OR(L115="",H115=""),"",IF(H115&lt;=0,"",IFERROR(L115/H115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="M116" s="17">
+        <f>IF(OR(M115="",I115=""),"",IF(I115&lt;=0,"",IFERROR(M115/I115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="N116" s="17">
+        <f>IF(OR(N115="",J115=""),"",IF(J115&lt;=0,"",IFERROR(N115/J115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="U116" s="17">
+        <f>IF(OR(U115="",T115=""),"",IF(T115&lt;=0,"",IFERROR(U115/T115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="V116" s="17">
+        <f>IF(OR(V115="",U115=""),"",IF(U115&lt;=0,"",IFERROR(V115/U115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="W116" s="17">
+        <f>IF(OR(W115="",V115=""),"",IF(V115&lt;=0,"",IFERROR(W115/V115-1,"")))</f>
+        <v/>
+      </c>
+      <c r="X116" s="17">
+        <f>IF(OR(X115="",W115=""),"",IF(W115&lt;=0,"",IFERROR(X115/W115-1,"")))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="18" t="inlineStr">
         <is>
           <t>현금흐름표 · 전 항목</t>
         </is>
       </c>
-      <c r="B112" s="44" t="inlineStr">
+      <c r="B118" s="44" t="inlineStr">
         <is>
           <t>분기 = 결산기 첫날부터 누계(공시 그대로)</t>
         </is>
       </c>
-      <c r="C112" s="18" t="n"/>
-      <c r="D112" s="18" t="n"/>
-      <c r="E112" s="18" t="n"/>
-      <c r="F112" s="18" t="n"/>
-      <c r="G112" s="18" t="n"/>
-      <c r="H112" s="18" t="n"/>
-      <c r="I112" s="18" t="n"/>
-      <c r="J112" s="18" t="n"/>
-      <c r="K112" s="18" t="n"/>
-      <c r="L112" s="18" t="n"/>
-      <c r="M112" s="18" t="n"/>
-      <c r="N112" s="18" t="n"/>
-      <c r="O112" s="18" t="n"/>
-      <c r="P112" s="18" t="n"/>
-      <c r="Q112" s="18" t="n"/>
-      <c r="R112" s="18" t="n"/>
-      <c r="S112" s="18" t="n"/>
-      <c r="T112" s="18" t="n"/>
-      <c r="U112" s="18" t="n"/>
-      <c r="V112" s="18" t="n"/>
-      <c r="W112" s="18" t="n"/>
-      <c r="X112" s="18" t="n"/>
-      <c r="Y112" s="18" t="n"/>
-      <c r="Z112" s="18" t="n"/>
-      <c r="AA112" s="18" t="n"/>
-      <c r="AB112" s="18" t="n"/>
-      <c r="AC112" s="18" t="n"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="5" t="inlineStr">
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="18" t="n"/>
+      <c r="I118" s="18" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
+      <c r="L118" s="18" t="n"/>
+      <c r="M118" s="18" t="n"/>
+      <c r="N118" s="18" t="n"/>
+      <c r="O118" s="18" t="n"/>
+      <c r="P118" s="18" t="n"/>
+      <c r="Q118" s="18" t="n"/>
+      <c r="R118" s="18" t="n"/>
+      <c r="S118" s="18" t="n"/>
+      <c r="T118" s="18" t="n"/>
+      <c r="U118" s="18" t="n"/>
+      <c r="V118" s="18" t="n"/>
+      <c r="W118" s="18" t="n"/>
+      <c r="X118" s="18" t="n"/>
+      <c r="Y118" s="18" t="n"/>
+      <c r="Z118" s="18" t="n"/>
+      <c r="AA118" s="18" t="n"/>
+      <c r="AB118" s="18" t="n"/>
+      <c r="AC118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B119" s="5" t="inlineStr">
         <is>
           <t>참고</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C119" s="5" t="inlineStr">
         <is>
           <t>2023.4Q</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D119" s="5" t="inlineStr">
         <is>
           <t>2024.1Q</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E119" s="5" t="inlineStr">
         <is>
           <t>2024.2Q</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F119" s="5" t="inlineStr">
         <is>
           <t>2024.3Q</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G119" s="5" t="inlineStr">
         <is>
           <t>2024.4Q</t>
         </is>
       </c>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H119" s="5" t="inlineStr">
         <is>
           <t>2025.1Q</t>
         </is>
       </c>
-      <c r="I113" s="5" t="inlineStr">
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>2025.2Q</t>
         </is>
       </c>
-      <c r="J113" s="5" t="inlineStr">
+      <c r="J119" s="5" t="inlineStr">
         <is>
           <t>2025.3Q</t>
         </is>
       </c>
-      <c r="K113" s="5" t="inlineStr">
+      <c r="K119" s="5" t="inlineStr">
         <is>
           <t>2025.4Q</t>
         </is>
       </c>
-      <c r="L113" s="5" t="inlineStr">
+      <c r="L119" s="5" t="inlineStr">
         <is>
           <t>2026.1Q</t>
         </is>
       </c>
-      <c r="M113" s="5" t="inlineStr">
+      <c r="M119" s="5" t="inlineStr">
         <is>
           <t>2026.2Q</t>
         </is>
       </c>
-      <c r="N113" s="5" t="inlineStr">
+      <c r="N119" s="5" t="inlineStr">
         <is>
           <t>2026.3Q</t>
         </is>
       </c>
-      <c r="O113" s="5" t="inlineStr">
+      <c r="O119" s="5" t="inlineStr">
         <is>
           <t>2016</t>
         </is>
       </c>
-      <c r="P113" s="5" t="inlineStr">
+      <c r="P119" s="5" t="inlineStr">
         <is>
           <t>2017</t>
         </is>
       </c>
-      <c r="Q113" s="5" t="inlineStr">
+      <c r="Q119" s="5" t="inlineStr">
         <is>
           <t>2018</t>
         </is>
       </c>
-      <c r="R113" s="5" t="inlineStr">
+      <c r="R119" s="5" t="inlineStr">
         <is>
           <t>2019</t>
         </is>
       </c>
-      <c r="S113" s="5" t="inlineStr">
+      <c r="S119" s="5" t="inlineStr">
         <is>
           <t>2020</t>
         </is>
       </c>
-      <c r="T113" s="5" t="inlineStr">
+      <c r="T119" s="5" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="U113" s="5" t="inlineStr">
+      <c r="U119" s="5" t="inlineStr">
         <is>
           <t>2022</t>
         </is>
       </c>
-      <c r="V113" s="5" t="inlineStr">
+      <c r="V119" s="5" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="W113" s="5" t="inlineStr">
+      <c r="W119" s="5" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="X113" s="5" t="inlineStr">
+      <c r="X119" s="5" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="Y113" s="5" t="inlineStr">
+      <c r="Y119" s="5" t="inlineStr">
         <is>
           <t>2026(MW)</t>
         </is>
       </c>
-      <c r="Z113" s="5" t="inlineStr">
+      <c r="Z119" s="5" t="inlineStr">
         <is>
           <t>2027(MW)</t>
         </is>
       </c>
-      <c r="AA113" s="5" t="inlineStr">
+      <c r="AA119" s="5" t="inlineStr">
         <is>
           <t>2028(MW)</t>
         </is>
       </c>
-      <c r="AB113" s="5" t="inlineStr">
+      <c r="AB119" s="5" t="inlineStr">
         <is>
           <t>2029(MW)</t>
         </is>
       </c>
-      <c r="AC113" s="5" t="inlineStr">
+      <c r="AC119" s="5" t="inlineStr">
         <is>
           <t>2030(MW)</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="9" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="9" t="inlineStr">
         <is>
           <t>법인세차감전 순이익</t>
         </is>
       </c>
-      <c r="C114" s="12" t="n">
+      <c r="C120" s="12" t="n">
         <v>-503.768</v>
       </c>
-      <c r="E114" s="12" t="n">
+      <c r="E120" s="12" t="n">
         <v>-93.46899999999999</v>
       </c>
-      <c r="G114" s="12" t="n">
+      <c r="G120" s="12" t="n">
         <v>-132.152</v>
       </c>
-      <c r="I114" s="12" t="n">
+      <c r="I120" s="12" t="n">
         <v>272.65</v>
       </c>
-      <c r="K114" s="12" t="n">
+      <c r="K120" s="12" t="n">
         <v>425.146</v>
       </c>
-      <c r="M114" s="12" t="n">
+      <c r="M120" s="12" t="n">
         <v>548.468</v>
       </c>
-      <c r="R114" s="12" t="n">
+      <c r="R120" s="12" t="n">
         <v>127.312</v>
       </c>
-      <c r="S114" s="12" t="n">
+      <c r="S120" s="12" t="n">
         <v>512.054</v>
       </c>
-      <c r="T114" s="12" t="n">
+      <c r="T120" s="12" t="n">
         <v>326.089</v>
       </c>
-      <c r="U114" s="12" t="n">
+      <c r="U120" s="12" t="n">
         <v>-1264.138</v>
       </c>
-      <c r="V114" s="12" t="n">
+      <c r="V120" s="12" t="n">
         <v>-503.768</v>
       </c>
-      <c r="W114" s="12" t="n">
+      <c r="W120" s="12" t="n">
         <v>-132.152</v>
       </c>
-      <c r="X114" s="12" t="n">
+      <c r="X120" s="12" t="n">
         <v>425.146</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="20" t="inlineStr">
-        <is>
-          <t>감가상각비</t>
-        </is>
-      </c>
-      <c r="C115" s="22" t="n">
-        <v>28.459</v>
-      </c>
-      <c r="E115" s="22" t="n">
-        <v>49.502</v>
-      </c>
-      <c r="G115" s="22" t="n">
-        <v>118.854</v>
-      </c>
-      <c r="I115" s="22" t="n">
-        <v>83.645</v>
-      </c>
-      <c r="K115" s="22" t="n">
-        <v>177.763</v>
-      </c>
-      <c r="M115" s="22" t="n">
-        <v>102.044</v>
-      </c>
-      <c r="R115" s="22" t="n">
-        <v>30.515</v>
-      </c>
-      <c r="S115" s="22" t="n">
-        <v>65.40900000000001</v>
-      </c>
-      <c r="T115" s="22" t="n">
-        <v>99.30500000000001</v>
-      </c>
-      <c r="U115" s="22" t="n">
-        <v>157.24</v>
-      </c>
-      <c r="V115" s="22" t="n">
-        <v>28.459</v>
-      </c>
-      <c r="W115" s="22" t="n">
-        <v>118.854</v>
-      </c>
-      <c r="X115" s="22" t="n">
-        <v>177.763</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="20" t="inlineStr">
-        <is>
-          <t>손상차손</t>
-        </is>
-      </c>
-      <c r="C116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K116" s="22" t="n">
-        <v>18.607</v>
-      </c>
-      <c r="M116" s="22" t="n">
-        <v>20.492</v>
-      </c>
-      <c r="T116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U116" s="22" t="n">
-        <v>1009.307</v>
-      </c>
-      <c r="V116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X116" s="22" t="n">
-        <v>18.607</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="20" t="inlineStr">
-        <is>
-          <t>영업권 상각</t>
-        </is>
-      </c>
-      <c r="C117" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S117" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T117" s="22" t="n">
-        <v>2.666</v>
-      </c>
-      <c r="U117" s="22" t="n">
-        <v>4</v>
-      </c>
-      <c r="V117" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="20" t="inlineStr">
-        <is>
-          <t>주식교부비 상각</t>
-        </is>
-      </c>
-      <c r="C118" s="22" t="n">
-        <v>6.961</v>
-      </c>
-      <c r="E118" s="22" t="n">
-        <v>1.924</v>
-      </c>
-      <c r="G118" s="22" t="n">
-        <v>1.924</v>
-      </c>
-      <c r="I118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S118" s="22" t="n">
-        <v>4.515</v>
-      </c>
-      <c r="T118" s="22" t="n">
-        <v>9.548999999999999</v>
-      </c>
-      <c r="U118" s="22" t="n">
-        <v>11.51</v>
-      </c>
-      <c r="V118" s="22" t="n">
-        <v>6.961</v>
-      </c>
-      <c r="W118" s="22" t="n">
-        <v>1.924</v>
-      </c>
-      <c r="X118" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="20" t="inlineStr">
-        <is>
-          <t>대손충당금 증감</t>
-        </is>
-      </c>
-      <c r="E119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="22" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="K119" s="22" t="n">
-        <v>0.083</v>
-      </c>
-      <c r="M119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R119" s="22" t="n">
-        <v>3.469</v>
-      </c>
-      <c r="S119" s="22" t="n">
-        <v>3.426</v>
-      </c>
-      <c r="T119" s="22" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="U119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X119" s="22" t="n">
-        <v>0.083</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="20" t="inlineStr">
-        <is>
-          <t>퇴직급여충당금 증감액</t>
-        </is>
-      </c>
-      <c r="C120" s="22" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="E120" s="22" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="G120" s="22" t="n">
-        <v>1.547</v>
-      </c>
-      <c r="I120" s="22" t="n">
-        <v>-0.9419999999999999</v>
-      </c>
-      <c r="K120" s="22" t="n">
-        <v>-0.953</v>
-      </c>
-      <c r="M120" s="22" t="n">
-        <v>-2.916</v>
-      </c>
-      <c r="S120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T120" s="22" t="n">
-        <v>0.337</v>
-      </c>
-      <c r="U120" s="22" t="n">
-        <v>1.321</v>
-      </c>
-      <c r="V120" s="22" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="W120" s="22" t="n">
-        <v>1.547</v>
-      </c>
-      <c r="X120" s="22" t="n">
-        <v>-0.953</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="20" t="inlineStr">
         <is>
-          <t>근속 인센티브 충당금 증감액</t>
+          <t>감가상각비</t>
         </is>
       </c>
       <c r="C121" s="22" t="n">
-        <v>-5.553</v>
+        <v>28.459</v>
       </c>
       <c r="E121" s="22" t="n">
-        <v>-6.18</v>
+        <v>49.502</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>-9.6</v>
+        <v>118.854</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>-6.84</v>
+        <v>83.645</v>
       </c>
       <c r="K121" s="22" t="n">
-        <v>5.811</v>
+        <v>177.763</v>
       </c>
       <c r="M121" s="22" t="n">
-        <v>13.96</v>
+        <v>102.044</v>
       </c>
       <c r="R121" s="22" t="n">
-        <v>5.896</v>
+        <v>30.515</v>
       </c>
       <c r="S121" s="22" t="n">
-        <v>13.078</v>
+        <v>65.40900000000001</v>
       </c>
       <c r="T121" s="22" t="n">
-        <v>14.18</v>
+        <v>99.30500000000001</v>
       </c>
       <c r="U121" s="22" t="n">
-        <v>18.169</v>
+        <v>157.24</v>
       </c>
       <c r="V121" s="22" t="n">
-        <v>-5.553</v>
+        <v>28.459</v>
       </c>
       <c r="W121" s="22" t="n">
-        <v>-9.6</v>
+        <v>118.854</v>
       </c>
       <c r="X121" s="22" t="n">
-        <v>5.811</v>
+        <v>177.763</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="20" t="inlineStr">
         <is>
-          <t>이자비용</t>
-        </is>
-      </c>
-      <c r="R122" s="22" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="S122" s="22" t="n">
-        <v>0.111</v>
+          <t>손상차손</t>
+        </is>
+      </c>
+      <c r="C122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="22" t="n">
+        <v>18.607</v>
+      </c>
+      <c r="M122" s="22" t="n">
+        <v>20.492</v>
       </c>
       <c r="T122" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="U122" s="22" t="n">
+        <v>1009.307</v>
+      </c>
+      <c r="V122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W122" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X122" s="22" t="n">
+        <v>18.607</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수익</t>
+          <t>영업권 상각</t>
         </is>
       </c>
       <c r="C123" s="22" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="E123" s="22" t="n">
-        <v>-0.004</v>
-      </c>
-      <c r="G123" s="22" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="I123" s="22" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="K123" s="22" t="n">
-        <v>-0.041</v>
-      </c>
-      <c r="M123" s="22" t="n">
-        <v>-0.02</v>
+        <v>0</v>
+      </c>
+      <c r="S123" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T123" s="22" t="n">
-        <v>0</v>
+        <v>2.666</v>
       </c>
       <c r="U123" s="22" t="n">
-        <v>-0.02</v>
+        <v>4</v>
       </c>
       <c r="V123" s="22" t="n">
-        <v>-0.044</v>
-      </c>
-      <c r="W123" s="22" t="n">
-        <v>-0.031</v>
-      </c>
-      <c r="X123" s="22" t="n">
-        <v>-0.041</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 평가손익</t>
+          <t>주식교부비 상각</t>
         </is>
       </c>
       <c r="C124" s="22" t="n">
-        <v>24.397</v>
+        <v>6.961</v>
+      </c>
+      <c r="E124" s="22" t="n">
+        <v>1.924</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>78.23999999999999</v>
+        <v>1.924</v>
+      </c>
+      <c r="I124" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="K124" s="22" t="n">
-        <v>35.744</v>
+        <v>0</v>
+      </c>
+      <c r="R124" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" s="22" t="n">
+        <v>4.515</v>
       </c>
       <c r="T124" s="22" t="n">
-        <v>0</v>
+        <v>9.548999999999999</v>
       </c>
       <c r="U124" s="22" t="n">
-        <v>49.768</v>
+        <v>11.51</v>
       </c>
       <c r="V124" s="22" t="n">
-        <v>24.397</v>
+        <v>6.961</v>
       </c>
       <c r="W124" s="22" t="n">
-        <v>78.23999999999999</v>
+        <v>1.924</v>
       </c>
       <c r="X124" s="22" t="n">
-        <v>35.744</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="20" t="inlineStr">
         <is>
-          <t>고정자산 매각손익</t>
-        </is>
-      </c>
-      <c r="C125" s="22" t="n">
+          <t>대손충당금 증감</t>
+        </is>
+      </c>
+      <c r="E125" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>-0.111</v>
+        <v>0</v>
+      </c>
+      <c r="I125" s="22" t="n">
+        <v>0.083</v>
       </c>
       <c r="K125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V125" s="22" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="M125" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" s="22" t="n">
+        <v>3.469</v>
+      </c>
+      <c r="S125" s="22" t="n">
+        <v>3.426</v>
+      </c>
+      <c r="T125" s="22" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="U125" s="22" t="n">
         <v>0</v>
       </c>
       <c r="W125" s="22" t="n">
-        <v>-0.111</v>
+        <v>0</v>
       </c>
       <c r="X125" s="22" t="n">
-        <v>0</v>
+        <v>0.083</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="20" t="inlineStr">
         <is>
-          <t>매출채권 증감</t>
+          <t>퇴직급여충당금 증감액</t>
         </is>
       </c>
       <c r="C126" s="22" t="n">
-        <v>-144.431</v>
+        <v>0.776</v>
       </c>
       <c r="E126" s="22" t="n">
-        <v>44.69</v>
+        <v>0.795</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>63.057</v>
+        <v>1.547</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>-126.675</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="K126" s="22" t="n">
-        <v>-78.804</v>
+        <v>-0.953</v>
       </c>
       <c r="M126" s="22" t="n">
-        <v>-94.572</v>
-      </c>
-      <c r="R126" s="22" t="n">
-        <v>-55.479</v>
+        <v>-2.916</v>
       </c>
       <c r="S126" s="22" t="n">
-        <v>-335.624</v>
+        <v>0</v>
       </c>
       <c r="T126" s="22" t="n">
-        <v>-21.011</v>
+        <v>0.337</v>
       </c>
       <c r="U126" s="22" t="n">
-        <v>212.002</v>
+        <v>1.321</v>
       </c>
       <c r="V126" s="22" t="n">
-        <v>-144.431</v>
+        <v>0.776</v>
       </c>
       <c r="W126" s="22" t="n">
-        <v>63.057</v>
+        <v>1.547</v>
       </c>
       <c r="X126" s="22" t="n">
-        <v>-78.804</v>
+        <v>-0.953</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각손익</t>
+          <t>근속 인센티브 충당금 증감액</t>
         </is>
       </c>
       <c r="C127" s="22" t="n">
-        <v>0</v>
+        <v>-5.553</v>
+      </c>
+      <c r="E127" s="22" t="n">
+        <v>-6.18</v>
+      </c>
+      <c r="G127" s="22" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="I127" s="22" t="n">
+        <v>-6.84</v>
+      </c>
+      <c r="K127" s="22" t="n">
+        <v>5.811</v>
+      </c>
+      <c r="M127" s="22" t="n">
+        <v>13.96</v>
+      </c>
+      <c r="R127" s="22" t="n">
+        <v>5.896</v>
+      </c>
+      <c r="S127" s="22" t="n">
+        <v>13.078</v>
       </c>
       <c r="T127" s="22" t="n">
-        <v>0</v>
+        <v>14.18</v>
       </c>
       <c r="U127" s="22" t="n">
-        <v>-97.5</v>
+        <v>18.169</v>
       </c>
       <c r="V127" s="22" t="n">
-        <v>0</v>
+        <v>-5.553</v>
+      </c>
+      <c r="W127" s="22" t="n">
+        <v>-9.6</v>
+      </c>
+      <c r="X127" s="22" t="n">
+        <v>5.811</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="20" t="inlineStr">
         <is>
-          <t>신주예약권 환입이익</t>
-        </is>
-      </c>
-      <c r="C128" s="22" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="E128" s="22" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="G128" s="22" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="I128" s="22" t="n">
-        <v>-9.765000000000001</v>
-      </c>
-      <c r="K128" s="22" t="n">
-        <v>-9.765000000000001</v>
-      </c>
-      <c r="M128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" s="22" t="n">
-        <v>-3.1</v>
-      </c>
-      <c r="W128" s="22" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="X128" s="22" t="n">
-        <v>-9.765000000000001</v>
+          <t>이자비용</t>
+        </is>
+      </c>
+      <c r="R128" s="22" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="S128" s="22" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="T128" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="20" t="inlineStr">
         <is>
-          <t>선수금 증감</t>
+          <t>이자·배당금 수익</t>
         </is>
       </c>
       <c r="C129" s="22" t="n">
-        <v>3.436</v>
+        <v>-0.044</v>
       </c>
       <c r="E129" s="22" t="n">
-        <v>-4.211</v>
+        <v>-0.004</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>2.819</v>
+        <v>-0.031</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>-2.574</v>
+        <v>-0.02</v>
       </c>
       <c r="K129" s="22" t="n">
-        <v>1.543</v>
+        <v>-0.041</v>
       </c>
       <c r="M129" s="22" t="n">
-        <v>3.566</v>
+        <v>-0.02</v>
       </c>
       <c r="T129" s="22" t="n">
         <v>0</v>
       </c>
       <c r="U129" s="22" t="n">
-        <v>0.775</v>
+        <v>-0.02</v>
       </c>
       <c r="V129" s="22" t="n">
-        <v>3.436</v>
+        <v>-0.044</v>
       </c>
       <c r="W129" s="22" t="n">
-        <v>2.819</v>
+        <v>-0.031</v>
       </c>
       <c r="X129" s="22" t="n">
-        <v>1.543</v>
+        <v>-0.041</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="20" t="inlineStr">
         <is>
-          <t>미지급금 증감</t>
+          <t>투자유가증권 평가손익</t>
         </is>
       </c>
       <c r="C130" s="22" t="n">
-        <v>-1.391</v>
-      </c>
-      <c r="E130" s="22" t="n">
-        <v>-76.84999999999999</v>
+        <v>24.397</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>-96.149</v>
-      </c>
-      <c r="I130" s="22" t="n">
-        <v>42.086</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="K130" s="22" t="n">
-        <v>180.029</v>
-      </c>
-      <c r="M130" s="22" t="n">
-        <v>-52.445</v>
-      </c>
-      <c r="R130" s="22" t="n">
-        <v>76.819</v>
-      </c>
-      <c r="S130" s="22" t="n">
-        <v>663.177</v>
+        <v>35.744</v>
       </c>
       <c r="T130" s="22" t="n">
-        <v>-216.487</v>
+        <v>0</v>
       </c>
       <c r="U130" s="22" t="n">
-        <v>-222.312</v>
+        <v>49.768</v>
       </c>
       <c r="V130" s="22" t="n">
-        <v>-1.391</v>
+        <v>24.397</v>
       </c>
       <c r="W130" s="22" t="n">
-        <v>-96.149</v>
+        <v>78.23999999999999</v>
       </c>
       <c r="X130" s="22" t="n">
-        <v>180.029</v>
+        <v>35.744</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="20" t="inlineStr">
         <is>
-          <t>미지급비용 증감</t>
+          <t>고정자산 매각손익</t>
         </is>
       </c>
       <c r="C131" s="22" t="n">
-        <v>2.953</v>
-      </c>
-      <c r="E131" s="22" t="n">
-        <v>7.146</v>
+        <v>0</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>-5.438</v>
-      </c>
-      <c r="I131" s="22" t="n">
-        <v>-66.851</v>
+        <v>-0.111</v>
       </c>
       <c r="K131" s="22" t="n">
-        <v>-54.365</v>
-      </c>
-      <c r="M131" s="22" t="n">
-        <v>-0.674</v>
-      </c>
-      <c r="R131" s="22" t="n">
-        <v>-15.789</v>
-      </c>
-      <c r="S131" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="T131" s="22" t="n">
-        <v>-16.531</v>
-      </c>
-      <c r="U131" s="22" t="n">
-        <v>19.738</v>
+        <v>0</v>
       </c>
       <c r="V131" s="22" t="n">
-        <v>2.953</v>
+        <v>0</v>
       </c>
       <c r="W131" s="22" t="n">
-        <v>-5.438</v>
+        <v>-0.111</v>
       </c>
       <c r="X131" s="22" t="n">
-        <v>-54.365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="20" t="inlineStr">
         <is>
-          <t>예수금 증감</t>
+          <t>매출채권 증감</t>
         </is>
       </c>
       <c r="C132" s="22" t="n">
-        <v>162.674</v>
+        <v>-144.431</v>
       </c>
       <c r="E132" s="22" t="n">
-        <v>-1216.666</v>
+        <v>44.69</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>-1190.593</v>
+        <v>63.057</v>
       </c>
       <c r="I132" s="22" t="n">
-        <v>134.276</v>
+        <v>-126.675</v>
       </c>
       <c r="K132" s="22" t="n">
-        <v>200.079</v>
+        <v>-78.804</v>
       </c>
       <c r="M132" s="22" t="n">
-        <v>373.688</v>
+        <v>-94.572</v>
       </c>
       <c r="R132" s="22" t="n">
-        <v>293.393</v>
+        <v>-55.479</v>
       </c>
       <c r="S132" s="22" t="n">
-        <v>1544.786</v>
+        <v>-335.624</v>
       </c>
       <c r="T132" s="22" t="n">
-        <v>306.858</v>
+        <v>-21.011</v>
       </c>
       <c r="U132" s="22" t="n">
-        <v>-514.069</v>
+        <v>212.002</v>
       </c>
       <c r="V132" s="22" t="n">
-        <v>162.674</v>
+        <v>-144.431</v>
       </c>
       <c r="W132" s="22" t="n">
-        <v>-1190.593</v>
+        <v>63.057</v>
       </c>
       <c r="X132" s="22" t="n">
-        <v>200.079</v>
+        <v>-78.804</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="20" t="inlineStr">
         <is>
-          <t>미지급 소비세 증감</t>
-        </is>
-      </c>
-      <c r="R133" s="22" t="n">
-        <v>-24.097</v>
-      </c>
-      <c r="S133" s="22" t="n">
-        <v>92.017</v>
+          <t>투자유가증권 매각손익</t>
+        </is>
+      </c>
+      <c r="C133" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T133" s="22" t="n">
-        <v>-49.972</v>
+        <v>0</v>
       </c>
       <c r="U133" s="22" t="n">
-        <v>-57.66</v>
+        <v>-97.5</v>
+      </c>
+      <c r="V133" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="20" t="inlineStr">
         <is>
-          <t>미지급·미수 소비세 증감액</t>
+          <t>신주예약권 환입이익</t>
         </is>
       </c>
       <c r="C134" s="22" t="n">
-        <v>4.134</v>
+        <v>-3.1</v>
       </c>
       <c r="E134" s="22" t="n">
-        <v>46.137</v>
+        <v>-3.1</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>87.246</v>
+        <v>-6.2</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>-18.571</v>
+        <v>-9.765000000000001</v>
       </c>
       <c r="K134" s="22" t="n">
-        <v>30.483</v>
+        <v>-9.765000000000001</v>
       </c>
       <c r="M134" s="22" t="n">
-        <v>-40.272</v>
+        <v>0</v>
       </c>
       <c r="U134" s="22" t="n">
-        <v>-57.66</v>
+        <v>0</v>
       </c>
       <c r="V134" s="22" t="n">
-        <v>4.134</v>
+        <v>-3.1</v>
       </c>
       <c r="W134" s="22" t="n">
-        <v>87.246</v>
+        <v>-6.2</v>
       </c>
       <c r="X134" s="22" t="n">
-        <v>30.483</v>
+        <v>-9.765000000000001</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="20" t="inlineStr">
         <is>
-          <t>기타</t>
+          <t>선수금 증감</t>
         </is>
       </c>
       <c r="C135" s="22" t="n">
-        <v>36.094</v>
+        <v>3.436</v>
       </c>
       <c r="E135" s="22" t="n">
-        <v>32.455</v>
+        <v>-4.211</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>2.63</v>
+        <v>2.819</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>2.04</v>
+        <v>-2.574</v>
       </c>
       <c r="K135" s="22" t="n">
-        <v>64.56100000000001</v>
+        <v>1.543</v>
       </c>
       <c r="M135" s="22" t="n">
-        <v>-11.982</v>
-      </c>
-      <c r="R135" s="22" t="n">
-        <v>3.856</v>
-      </c>
-      <c r="S135" s="22" t="n">
-        <v>20.756</v>
+        <v>3.566</v>
       </c>
       <c r="T135" s="22" t="n">
-        <v>-89.10599999999999</v>
+        <v>0</v>
       </c>
       <c r="U135" s="22" t="n">
-        <v>-58.754</v>
+        <v>0.775</v>
       </c>
       <c r="V135" s="22" t="n">
-        <v>36.094</v>
+        <v>3.436</v>
       </c>
       <c r="W135" s="22" t="n">
-        <v>2.63</v>
+        <v>2.819</v>
       </c>
       <c r="X135" s="22" t="n">
-        <v>64.56100000000001</v>
+        <v>1.543</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="20" t="inlineStr">
         <is>
-          <t>소계</t>
+          <t>미지급금 증감</t>
         </is>
       </c>
       <c r="C136" s="22" t="n">
-        <v>-388.401</v>
+        <v>-1.391</v>
       </c>
       <c r="E136" s="22" t="n">
-        <v>-1217.828</v>
+        <v>-76.84999999999999</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>-1083.953</v>
+        <v>-96.149</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>302.541</v>
+        <v>42.086</v>
       </c>
       <c r="K136" s="22" t="n">
-        <v>995.927</v>
+        <v>180.029</v>
       </c>
       <c r="M136" s="22" t="n">
-        <v>859.336</v>
+        <v>-52.445</v>
       </c>
       <c r="R136" s="22" t="n">
-        <v>446.266</v>
+        <v>76.819</v>
       </c>
       <c r="S136" s="22" t="n">
-        <v>2611.71</v>
+        <v>663.177</v>
       </c>
       <c r="T136" s="22" t="n">
-        <v>366.163</v>
+        <v>-216.487</v>
       </c>
       <c r="U136" s="22" t="n">
-        <v>-730.621</v>
+        <v>-222.312</v>
       </c>
       <c r="V136" s="22" t="n">
-        <v>-388.401</v>
+        <v>-1.391</v>
       </c>
       <c r="W136" s="22" t="n">
-        <v>-1083.953</v>
+        <v>-96.149</v>
       </c>
       <c r="X136" s="22" t="n">
-        <v>995.927</v>
+        <v>180.029</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="20" t="inlineStr">
         <is>
-          <t>이자 지급</t>
-        </is>
+          <t>미지급비용 증감</t>
+        </is>
+      </c>
+      <c r="C137" s="22" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="E137" s="22" t="n">
+        <v>7.146</v>
+      </c>
+      <c r="G137" s="22" t="n">
+        <v>-5.438</v>
+      </c>
+      <c r="I137" s="22" t="n">
+        <v>-66.851</v>
+      </c>
+      <c r="K137" s="22" t="n">
+        <v>-54.365</v>
+      </c>
+      <c r="M137" s="22" t="n">
+        <v>-0.674</v>
       </c>
       <c r="R137" s="22" t="n">
-        <v>-0.354</v>
+        <v>-15.789</v>
       </c>
       <c r="S137" s="22" t="n">
-        <v>-0.097</v>
+        <v>28</v>
       </c>
       <c r="T137" s="22" t="n">
-        <v>0</v>
+        <v>-16.531</v>
+      </c>
+      <c r="U137" s="22" t="n">
+        <v>19.738</v>
+      </c>
+      <c r="V137" s="22" t="n">
+        <v>2.953</v>
+      </c>
+      <c r="W137" s="22" t="n">
+        <v>-5.438</v>
+      </c>
+      <c r="X137" s="22" t="n">
+        <v>-54.365</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="20" t="inlineStr">
         <is>
-          <t>이자·배당금 수취</t>
+          <t>예수금 증감</t>
         </is>
       </c>
       <c r="C138" s="22" t="n">
-        <v>0.046</v>
+        <v>162.674</v>
       </c>
       <c r="E138" s="22" t="n">
-        <v>0.004</v>
+        <v>-1216.666</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>0.031</v>
+        <v>-1190.593</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>0.02</v>
+        <v>134.276</v>
       </c>
       <c r="K138" s="22" t="n">
-        <v>0.041</v>
+        <v>200.079</v>
       </c>
       <c r="M138" s="22" t="n">
-        <v>0.02</v>
+        <v>373.688</v>
+      </c>
+      <c r="R138" s="22" t="n">
+        <v>293.393</v>
+      </c>
+      <c r="S138" s="22" t="n">
+        <v>1544.786</v>
       </c>
       <c r="T138" s="22" t="n">
-        <v>0</v>
+        <v>306.858</v>
       </c>
       <c r="U138" s="22" t="n">
-        <v>0.019</v>
+        <v>-514.069</v>
       </c>
       <c r="V138" s="22" t="n">
-        <v>0.046</v>
+        <v>162.674</v>
       </c>
       <c r="W138" s="22" t="n">
-        <v>0.031</v>
+        <v>-1190.593</v>
       </c>
       <c r="X138" s="22" t="n">
-        <v>0.041</v>
+        <v>200.079</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="20" t="inlineStr">
         <is>
-          <t>법인세 납부</t>
-        </is>
-      </c>
-      <c r="C139" s="22" t="n">
-        <v>-2.588</v>
-      </c>
-      <c r="E139" s="22" t="n">
-        <v>-10.787</v>
-      </c>
-      <c r="G139" s="22" t="n">
-        <v>-10.787</v>
-      </c>
-      <c r="I139" s="22" t="n">
-        <v>-10.892</v>
-      </c>
-      <c r="K139" s="22" t="n">
-        <v>-10.892</v>
-      </c>
-      <c r="M139" s="22" t="n">
-        <v>-49.988</v>
+          <t>미지급 소비세 증감</t>
+        </is>
       </c>
       <c r="R139" s="22" t="n">
-        <v>-58.019</v>
+        <v>-24.097</v>
       </c>
       <c r="S139" s="22" t="n">
-        <v>-47.272</v>
+        <v>92.017</v>
       </c>
       <c r="T139" s="22" t="n">
-        <v>-214.897</v>
+        <v>-49.972</v>
       </c>
       <c r="U139" s="22" t="n">
-        <v>-96.758</v>
-      </c>
-      <c r="V139" s="22" t="n">
-        <v>-2.588</v>
-      </c>
-      <c r="W139" s="22" t="n">
-        <v>-10.787</v>
-      </c>
-      <c r="X139" s="22" t="n">
-        <v>-10.892</v>
+        <v>-57.66</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="20" t="inlineStr">
         <is>
-          <t>법인세 환급</t>
+          <t>미지급·미수 소비세 증감액</t>
         </is>
       </c>
       <c r="C140" s="22" t="n">
-        <v>51.725</v>
+        <v>4.134</v>
       </c>
       <c r="E140" s="22" t="n">
-        <v>0</v>
+        <v>46.137</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>0</v>
+        <v>87.246</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>0</v>
+        <v>-18.571</v>
       </c>
       <c r="K140" s="22" t="n">
-        <v>0</v>
+        <v>30.483</v>
       </c>
       <c r="M140" s="22" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="R140" s="22" t="n">
-        <v>0.459</v>
-      </c>
-      <c r="S140" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T140" s="22" t="n">
-        <v>0.148</v>
+        <v>-40.272</v>
       </c>
       <c r="U140" s="22" t="n">
-        <v>0.038</v>
+        <v>-57.66</v>
       </c>
       <c r="V140" s="22" t="n">
-        <v>51.725</v>
+        <v>4.134</v>
       </c>
       <c r="W140" s="22" t="n">
-        <v>0</v>
+        <v>87.246</v>
       </c>
       <c r="X140" s="22" t="n">
-        <v>0</v>
+        <v>30.483</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="9" t="inlineStr">
-        <is>
-          <t>영업활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C141" s="12" t="n">
-        <v>-339.218</v>
-      </c>
-      <c r="E141" s="12" t="n">
-        <v>-1228.611</v>
-      </c>
-      <c r="G141" s="12" t="n">
-        <v>-1094.71</v>
-      </c>
-      <c r="I141" s="12" t="n">
-        <v>291.67</v>
-      </c>
-      <c r="K141" s="12" t="n">
-        <v>985.077</v>
-      </c>
-      <c r="M141" s="12" t="n">
-        <v>809.587</v>
-      </c>
-      <c r="R141" s="12" t="n">
-        <v>388.352</v>
-      </c>
-      <c r="S141" s="12" t="n">
-        <v>2564.34</v>
-      </c>
-      <c r="T141" s="12" t="n">
-        <v>151.414</v>
-      </c>
-      <c r="U141" s="12" t="n">
-        <v>-827.321</v>
-      </c>
-      <c r="V141" s="12" t="n">
-        <v>-339.218</v>
-      </c>
-      <c r="W141" s="12" t="n">
-        <v>-1094.71</v>
-      </c>
-      <c r="X141" s="12" t="n">
-        <v>985.077</v>
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="C141" s="22" t="n">
+        <v>36.094</v>
+      </c>
+      <c r="E141" s="22" t="n">
+        <v>32.455</v>
+      </c>
+      <c r="G141" s="22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="I141" s="22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K141" s="22" t="n">
+        <v>64.56100000000001</v>
+      </c>
+      <c r="M141" s="22" t="n">
+        <v>-11.982</v>
+      </c>
+      <c r="R141" s="22" t="n">
+        <v>3.856</v>
+      </c>
+      <c r="S141" s="22" t="n">
+        <v>20.756</v>
+      </c>
+      <c r="T141" s="22" t="n">
+        <v>-89.10599999999999</v>
+      </c>
+      <c r="U141" s="22" t="n">
+        <v>-58.754</v>
+      </c>
+      <c r="V141" s="22" t="n">
+        <v>36.094</v>
+      </c>
+      <c r="W141" s="22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="X141" s="22" t="n">
+        <v>64.56100000000001</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="20" t="inlineStr">
         <is>
-          <t>유형자산 취득(설비투자)</t>
+          <t>소계</t>
         </is>
       </c>
       <c r="C142" s="22" t="n">
-        <v>-7.32</v>
+        <v>-388.401</v>
       </c>
       <c r="E142" s="22" t="n">
-        <v>-1.962</v>
+        <v>-1217.828</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>-2.72</v>
+        <v>-1083.953</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>-12.102</v>
+        <v>302.541</v>
       </c>
       <c r="K142" s="22" t="n">
-        <v>-13.911</v>
+        <v>995.927</v>
       </c>
       <c r="M142" s="22" t="n">
-        <v>-0.66</v>
+        <v>859.336</v>
       </c>
       <c r="R142" s="22" t="n">
-        <v>-56.449</v>
+        <v>446.266</v>
       </c>
       <c r="S142" s="22" t="n">
-        <v>-6.736</v>
+        <v>2611.71</v>
       </c>
       <c r="T142" s="22" t="n">
-        <v>-7.114</v>
+        <v>366.163</v>
       </c>
       <c r="U142" s="22" t="n">
-        <v>-20.546</v>
+        <v>-730.621</v>
       </c>
       <c r="V142" s="22" t="n">
-        <v>-7.32</v>
+        <v>-388.401</v>
       </c>
       <c r="W142" s="22" t="n">
-        <v>-2.72</v>
+        <v>-1083.953</v>
       </c>
       <c r="X142" s="22" t="n">
-        <v>-13.911</v>
+        <v>995.927</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="20" t="inlineStr">
         <is>
-          <t>유형자산 매각</t>
-        </is>
-      </c>
-      <c r="C143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G143" s="22" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="K143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W143" s="22" t="n">
-        <v>0.111</v>
-      </c>
-      <c r="X143" s="22" t="n">
+          <t>이자 지급</t>
+        </is>
+      </c>
+      <c r="R143" s="22" t="n">
+        <v>-0.354</v>
+      </c>
+      <c r="S143" s="22" t="n">
+        <v>-0.097</v>
+      </c>
+      <c r="T143" s="22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="20" t="inlineStr">
         <is>
-          <t>무형자산 취득</t>
+          <t>이자·배당금 수취</t>
         </is>
       </c>
       <c r="C144" s="22" t="n">
-        <v>-575.278</v>
+        <v>0.046</v>
       </c>
       <c r="E144" s="22" t="n">
-        <v>-220.418</v>
+        <v>0.004</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>-383.834</v>
+        <v>0.031</v>
       </c>
       <c r="I144" s="22" t="n">
-        <v>-103.661</v>
+        <v>0.02</v>
       </c>
       <c r="K144" s="22" t="n">
-        <v>-138.474</v>
+        <v>0.041</v>
       </c>
       <c r="M144" s="22" t="n">
-        <v>-27.09</v>
-      </c>
-      <c r="R144" s="22" t="n">
-        <v>-167.211</v>
-      </c>
-      <c r="S144" s="22" t="n">
-        <v>-213.397</v>
+        <v>0.02</v>
       </c>
       <c r="T144" s="22" t="n">
-        <v>-306.265</v>
+        <v>0</v>
       </c>
       <c r="U144" s="22" t="n">
-        <v>-488.544</v>
+        <v>0.019</v>
       </c>
       <c r="V144" s="22" t="n">
-        <v>-575.278</v>
+        <v>0.046</v>
       </c>
       <c r="W144" s="22" t="n">
-        <v>-383.834</v>
+        <v>0.031</v>
       </c>
       <c r="X144" s="22" t="n">
-        <v>-138.474</v>
+        <v>0.041</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 취득</t>
+          <t>법인세 납부</t>
         </is>
       </c>
       <c r="C145" s="22" t="n">
-        <v>0</v>
+        <v>-2.588</v>
+      </c>
+      <c r="E145" s="22" t="n">
+        <v>-10.787</v>
+      </c>
+      <c r="G145" s="22" t="n">
+        <v>-10.787</v>
+      </c>
+      <c r="I145" s="22" t="n">
+        <v>-10.892</v>
+      </c>
+      <c r="K145" s="22" t="n">
+        <v>-10.892</v>
+      </c>
+      <c r="M145" s="22" t="n">
+        <v>-49.988</v>
       </c>
       <c r="R145" s="22" t="n">
-        <v>0</v>
+        <v>-58.019</v>
       </c>
       <c r="S145" s="22" t="n">
-        <v>-10.001</v>
+        <v>-47.272</v>
       </c>
       <c r="T145" s="22" t="n">
-        <v>-148.731</v>
+        <v>-214.897</v>
       </c>
       <c r="U145" s="22" t="n">
-        <v>-80.02</v>
+        <v>-96.758</v>
       </c>
       <c r="V145" s="22" t="n">
-        <v>0</v>
+        <v>-2.588</v>
+      </c>
+      <c r="W145" s="22" t="n">
+        <v>-10.787</v>
+      </c>
+      <c r="X145" s="22" t="n">
+        <v>-10.892</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="20" t="inlineStr">
         <is>
-          <t>투자유가증권 매각</t>
+          <t>법인세 환급</t>
         </is>
       </c>
       <c r="C146" s="22" t="n">
+        <v>51.725</v>
+      </c>
+      <c r="E146" s="22" t="n">
         <v>0</v>
       </c>
       <c r="G146" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="I146" s="22" t="n">
+        <v>0</v>
+      </c>
       <c r="K146" s="22" t="n">
-        <v>10.038</v>
+        <v>0</v>
+      </c>
+      <c r="M146" s="22" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="R146" s="22" t="n">
+        <v>0.459</v>
+      </c>
+      <c r="S146" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="T146" s="22" t="n">
-        <v>0</v>
+        <v>0.148</v>
       </c>
       <c r="U146" s="22" t="n">
-        <v>112.5</v>
+        <v>0.038</v>
       </c>
       <c r="V146" s="22" t="n">
-        <v>0</v>
+        <v>51.725</v>
       </c>
       <c r="W146" s="22" t="n">
         <v>0</v>
       </c>
       <c r="X146" s="22" t="n">
-        <v>10.038</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="20" t="inlineStr">
-        <is>
-          <t>임차보증금·보증금 납입</t>
-        </is>
-      </c>
-      <c r="C147" s="22" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="G147" s="22" t="n">
-        <v>-14.605</v>
-      </c>
-      <c r="K147" s="22" t="n">
-        <v>-1.872</v>
-      </c>
-      <c r="R147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S147" s="22" t="n">
-        <v>-17.426</v>
-      </c>
-      <c r="T147" s="22" t="n">
-        <v>-124.301</v>
-      </c>
-      <c r="U147" s="22" t="n">
-        <v>-4.729</v>
-      </c>
-      <c r="V147" s="22" t="n">
-        <v>-0.65</v>
-      </c>
-      <c r="W147" s="22" t="n">
-        <v>-14.605</v>
-      </c>
-      <c r="X147" s="22" t="n">
-        <v>-1.872</v>
+      <c r="A147" s="9" t="inlineStr">
+        <is>
+          <t>영업활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="n">
+        <v>-339.218</v>
+      </c>
+      <c r="E147" s="12" t="n">
+        <v>-1228.611</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>-1094.71</v>
+      </c>
+      <c r="I147" s="12" t="n">
+        <v>291.67</v>
+      </c>
+      <c r="K147" s="12" t="n">
+        <v>985.077</v>
+      </c>
+      <c r="M147" s="12" t="n">
+        <v>809.587</v>
+      </c>
+      <c r="R147" s="12" t="n">
+        <v>388.352</v>
+      </c>
+      <c r="S147" s="12" t="n">
+        <v>2564.34</v>
+      </c>
+      <c r="T147" s="12" t="n">
+        <v>151.414</v>
+      </c>
+      <c r="U147" s="12" t="n">
+        <v>-827.321</v>
+      </c>
+      <c r="V147" s="12" t="n">
+        <v>-339.218</v>
+      </c>
+      <c r="W147" s="12" t="n">
+        <v>-1094.71</v>
+      </c>
+      <c r="X147" s="12" t="n">
+        <v>985.077</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="20" t="inlineStr">
         <is>
-          <t>임차보증금·보증금 회수</t>
+          <t>유형자산 취득(설비투자)</t>
         </is>
       </c>
       <c r="C148" s="22" t="n">
-        <v>1.13</v>
+        <v>-7.32</v>
       </c>
       <c r="E148" s="22" t="n">
-        <v>0.581</v>
+        <v>-1.962</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>124.336</v>
+        <v>-2.72</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>2.247</v>
+        <v>-12.102</v>
       </c>
       <c r="K148" s="22" t="n">
-        <v>62.798</v>
+        <v>-13.911</v>
       </c>
       <c r="M148" s="22" t="n">
-        <v>3.294</v>
+        <v>-0.66</v>
+      </c>
+      <c r="R148" s="22" t="n">
+        <v>-56.449</v>
+      </c>
+      <c r="S148" s="22" t="n">
+        <v>-6.736</v>
       </c>
       <c r="T148" s="22" t="n">
-        <v>0</v>
+        <v>-7.114</v>
       </c>
       <c r="U148" s="22" t="n">
-        <v>5.877</v>
+        <v>-20.546</v>
       </c>
       <c r="V148" s="22" t="n">
-        <v>1.13</v>
+        <v>-7.32</v>
       </c>
       <c r="W148" s="22" t="n">
-        <v>124.336</v>
+        <v>-2.72</v>
       </c>
       <c r="X148" s="22" t="n">
-        <v>62.798</v>
+        <v>-13.911</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="20" t="inlineStr">
         <is>
-          <t>출자금 납입</t>
+          <t>유형자산 매각</t>
         </is>
       </c>
       <c r="C149" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="T149" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U149" s="22" t="n">
-        <v>-0.33</v>
+      <c r="G149" s="22" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="K149" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="V149" s="22" t="n">
         <v>0</v>
       </c>
+      <c r="W149" s="22" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="X149" s="22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="9" t="inlineStr">
-        <is>
-          <t>투자활동 현금흐름</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="n">
-        <v>-582.1180000000001</v>
-      </c>
-      <c r="E150" s="12" t="n">
-        <v>-221.798</v>
-      </c>
-      <c r="G150" s="12" t="n">
-        <v>-276.713</v>
-      </c>
-      <c r="I150" s="12" t="n">
-        <v>-113.515</v>
-      </c>
-      <c r="K150" s="12" t="n">
-        <v>-81.42</v>
-      </c>
-      <c r="M150" s="12" t="n">
-        <v>-24.456</v>
-      </c>
-      <c r="R150" s="12" t="n">
-        <v>-223.661</v>
-      </c>
-      <c r="S150" s="12" t="n">
-        <v>-247.561</v>
-      </c>
-      <c r="T150" s="12" t="n">
-        <v>-586.413</v>
-      </c>
-      <c r="U150" s="12" t="n">
-        <v>-475.792</v>
-      </c>
-      <c r="V150" s="12" t="n">
-        <v>-582.1180000000001</v>
-      </c>
-      <c r="W150" s="12" t="n">
-        <v>-276.713</v>
-      </c>
-      <c r="X150" s="12" t="n">
-        <v>-81.42</v>
+      <c r="A150" s="20" t="inlineStr">
+        <is>
+          <t>무형자산 취득</t>
+        </is>
+      </c>
+      <c r="C150" s="22" t="n">
+        <v>-575.278</v>
+      </c>
+      <c r="E150" s="22" t="n">
+        <v>-220.418</v>
+      </c>
+      <c r="G150" s="22" t="n">
+        <v>-383.834</v>
+      </c>
+      <c r="I150" s="22" t="n">
+        <v>-103.661</v>
+      </c>
+      <c r="K150" s="22" t="n">
+        <v>-138.474</v>
+      </c>
+      <c r="M150" s="22" t="n">
+        <v>-27.09</v>
+      </c>
+      <c r="R150" s="22" t="n">
+        <v>-167.211</v>
+      </c>
+      <c r="S150" s="22" t="n">
+        <v>-213.397</v>
+      </c>
+      <c r="T150" s="22" t="n">
+        <v>-306.265</v>
+      </c>
+      <c r="U150" s="22" t="n">
+        <v>-488.544</v>
+      </c>
+      <c r="V150" s="22" t="n">
+        <v>-575.278</v>
+      </c>
+      <c r="W150" s="22" t="n">
+        <v>-383.834</v>
+      </c>
+      <c r="X150" s="22" t="n">
+        <v>-138.474</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="20" t="inlineStr">
         <is>
-          <t>주식 발행</t>
+          <t>투자유가증권 취득</t>
         </is>
       </c>
       <c r="C151" s="22" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="E151" s="22" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="G151" s="22" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="I151" s="22" t="n">
-        <v>4.532</v>
-      </c>
-      <c r="K151" s="22" t="n">
-        <v>4.532</v>
-      </c>
-      <c r="M151" s="22" t="n">
         <v>0</v>
       </c>
       <c r="R151" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S151" s="22" t="n">
-        <v>1990.848</v>
+        <v>-10.001</v>
       </c>
       <c r="T151" s="22" t="n">
-        <v>3915.475</v>
+        <v>-148.731</v>
       </c>
       <c r="U151" s="22" t="n">
-        <v>33.784</v>
+        <v>-80.02</v>
       </c>
       <c r="V151" s="22" t="n">
-        <v>14.008</v>
-      </c>
-      <c r="W151" s="22" t="n">
-        <v>18.54</v>
-      </c>
-      <c r="X151" s="22" t="n">
-        <v>4.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="20" t="inlineStr">
         <is>
-          <t>단기차입</t>
-        </is>
-      </c>
-      <c r="R152" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="S152" s="22" t="n">
-        <v>0</v>
+          <t>투자유가증권 매각</t>
+        </is>
+      </c>
+      <c r="C152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K152" s="22" t="n">
+        <v>10.038</v>
+      </c>
+      <c r="T152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U152" s="22" t="n">
+        <v>112.5</v>
+      </c>
+      <c r="V152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W152" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X152" s="22" t="n">
+        <v>10.038</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="20" t="inlineStr">
         <is>
-          <t>단기차입금 상환</t>
-        </is>
+          <t>임차보증금·보증금 납입</t>
+        </is>
+      </c>
+      <c r="C153" s="22" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="G153" s="22" t="n">
+        <v>-14.605</v>
+      </c>
+      <c r="K153" s="22" t="n">
+        <v>-1.872</v>
       </c>
       <c r="R153" s="22" t="n">
         <v>0</v>
       </c>
       <c r="S153" s="22" t="n">
-        <v>-50</v>
+        <v>-17.426</v>
       </c>
       <c r="T153" s="22" t="n">
-        <v>0</v>
+        <v>-124.301</v>
+      </c>
+      <c r="U153" s="22" t="n">
+        <v>-4.729</v>
+      </c>
+      <c r="V153" s="22" t="n">
+        <v>-0.65</v>
+      </c>
+      <c r="W153" s="22" t="n">
+        <v>-14.605</v>
+      </c>
+      <c r="X153" s="22" t="n">
+        <v>-1.872</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="20" t="inlineStr">
         <is>
-          <t>장기차입금 상환</t>
-        </is>
-      </c>
-      <c r="R154" s="22" t="n">
-        <v>-30</v>
-      </c>
-      <c r="S154" s="22" t="n">
-        <v>-27.5</v>
+          <t>임차보증금·보증금 회수</t>
+        </is>
+      </c>
+      <c r="C154" s="22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E154" s="22" t="n">
+        <v>0.581</v>
+      </c>
+      <c r="G154" s="22" t="n">
+        <v>124.336</v>
+      </c>
+      <c r="I154" s="22" t="n">
+        <v>2.247</v>
+      </c>
+      <c r="K154" s="22" t="n">
+        <v>62.798</v>
+      </c>
+      <c r="M154" s="22" t="n">
+        <v>3.294</v>
       </c>
       <c r="T154" s="22" t="n">
         <v>0</v>
+      </c>
+      <c r="U154" s="22" t="n">
+        <v>5.877</v>
+      </c>
+      <c r="V154" s="22" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W154" s="22" t="n">
+        <v>124.336</v>
+      </c>
+      <c r="X154" s="22" t="n">
+        <v>62.798</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="20" t="inlineStr">
         <is>
-          <t>자기주식 취득</t>
+          <t>출자금 납입</t>
         </is>
       </c>
       <c r="C155" s="22" t="n">
         <v>0</v>
       </c>
-      <c r="E155" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="G155" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="I155" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K155" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="R155" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S155" s="22" t="n">
-        <v>-0.115</v>
-      </c>
       <c r="T155" s="22" t="n">
-        <v>-0.384</v>
+        <v>0</v>
       </c>
       <c r="U155" s="22" t="n">
-        <v>-0.125</v>
+        <v>-0.33</v>
       </c>
       <c r="V155" s="22" t="n">
         <v>0</v>
-      </c>
-      <c r="W155" s="22" t="n">
-        <v>-0.033</v>
-      </c>
-      <c r="X155" s="22" t="n">
-        <v>-0.033</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="9" t="inlineStr">
         <is>
-          <t>재무활동 현금흐름</t>
+          <t>투자활동 현금흐름</t>
         </is>
       </c>
       <c r="C156" s="12" t="n">
-        <v>14.008</v>
+        <v>-582.1180000000001</v>
       </c>
       <c r="E156" s="12" t="n">
-        <v>13.974</v>
+        <v>-221.798</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>18.506</v>
+        <v>-276.713</v>
       </c>
       <c r="I156" s="12" t="n">
-        <v>4.532</v>
+        <v>-113.515</v>
       </c>
       <c r="K156" s="12" t="n">
-        <v>4.498</v>
+        <v>-81.42</v>
       </c>
       <c r="M156" s="12" t="n">
-        <v>0</v>
+        <v>-24.456</v>
       </c>
       <c r="R156" s="12" t="n">
-        <v>20</v>
+        <v>-223.661</v>
       </c>
       <c r="S156" s="12" t="n">
-        <v>1913.232</v>
+        <v>-247.561</v>
       </c>
       <c r="T156" s="12" t="n">
-        <v>3915.091</v>
+        <v>-586.413</v>
       </c>
       <c r="U156" s="12" t="n">
-        <v>33.658</v>
+        <v>-475.792</v>
       </c>
       <c r="V156" s="12" t="n">
-        <v>14.008</v>
+        <v>-582.1180000000001</v>
       </c>
       <c r="W156" s="12" t="n">
-        <v>18.506</v>
+        <v>-276.713</v>
       </c>
       <c r="X156" s="12" t="n">
-        <v>4.498</v>
+        <v>-81.42</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="20" t="inlineStr">
         <is>
-          <t>현금성자산 증감</t>
+          <t>주식 발행</t>
         </is>
       </c>
       <c r="C157" s="22" t="n">
-        <v>-907.328</v>
+        <v>14.008</v>
       </c>
       <c r="E157" s="22" t="n">
-        <v>-1436.436</v>
+        <v>14.008</v>
       </c>
       <c r="G157" s="22" t="n">
-        <v>-1352.917</v>
+        <v>18.54</v>
       </c>
       <c r="I157" s="22" t="n">
-        <v>182.686</v>
+        <v>4.532</v>
       </c>
       <c r="K157" s="22" t="n">
-        <v>908.154</v>
+        <v>4.532</v>
       </c>
       <c r="M157" s="22" t="n">
-        <v>785.13</v>
+        <v>0</v>
       </c>
       <c r="R157" s="22" t="n">
-        <v>184.691</v>
+        <v>0</v>
       </c>
       <c r="S157" s="22" t="n">
-        <v>4230.011</v>
+        <v>1990.848</v>
       </c>
       <c r="T157" s="22" t="n">
-        <v>3480.092</v>
+        <v>3915.475</v>
       </c>
       <c r="U157" s="22" t="n">
-        <v>-1269.455</v>
+        <v>33.784</v>
       </c>
       <c r="V157" s="22" t="n">
-        <v>-907.328</v>
+        <v>14.008</v>
       </c>
       <c r="W157" s="22" t="n">
-        <v>-1352.917</v>
+        <v>18.54</v>
       </c>
       <c r="X157" s="22" t="n">
-        <v>908.154</v>
+        <v>4.532</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="20" t="inlineStr">
         <is>
+          <t>단기차입</t>
+        </is>
+      </c>
+      <c r="R158" s="22" t="n">
+        <v>50</v>
+      </c>
+      <c r="S158" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="20" t="inlineStr">
+        <is>
+          <t>단기차입금 상환</t>
+        </is>
+      </c>
+      <c r="R159" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S159" s="22" t="n">
+        <v>-50</v>
+      </c>
+      <c r="T159" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="20" t="inlineStr">
+        <is>
+          <t>장기차입금 상환</t>
+        </is>
+      </c>
+      <c r="R160" s="22" t="n">
+        <v>-30</v>
+      </c>
+      <c r="S160" s="22" t="n">
+        <v>-27.5</v>
+      </c>
+      <c r="T160" s="22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="20" t="inlineStr">
+        <is>
+          <t>자기주식 취득</t>
+        </is>
+      </c>
+      <c r="C161" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E161" s="22" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="G161" s="22" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="I161" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="22" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="R161" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S161" s="22" t="n">
+        <v>-0.115</v>
+      </c>
+      <c r="T161" s="22" t="n">
+        <v>-0.384</v>
+      </c>
+      <c r="U161" s="22" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="V161" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W161" s="22" t="n">
+        <v>-0.033</v>
+      </c>
+      <c r="X161" s="22" t="n">
+        <v>-0.033</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="9" t="inlineStr">
+        <is>
+          <t>재무활동 현금흐름</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="E162" s="12" t="n">
+        <v>13.974</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>18.506</v>
+      </c>
+      <c r="I162" s="12" t="n">
+        <v>4.532</v>
+      </c>
+      <c r="K162" s="12" t="n">
+        <v>4.498</v>
+      </c>
+      <c r="M162" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="S162" s="12" t="n">
+        <v>1913.232</v>
+      </c>
+      <c r="T162" s="12" t="n">
+        <v>3915.091</v>
+      </c>
+      <c r="U162" s="12" t="n">
+        <v>33.658</v>
+      </c>
+      <c r="V162" s="12" t="n">
+        <v>14.008</v>
+      </c>
+      <c r="W162" s="12" t="n">
+        <v>18.506</v>
+      </c>
+      <c r="X162" s="12" t="n">
+        <v>4.498</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="20" t="inlineStr">
+        <is>
+          <t>현금성자산 증감</t>
+        </is>
+      </c>
+      <c r="C163" s="22" t="n">
+        <v>-907.328</v>
+      </c>
+      <c r="E163" s="22" t="n">
+        <v>-1436.436</v>
+      </c>
+      <c r="G163" s="22" t="n">
+        <v>-1352.917</v>
+      </c>
+      <c r="I163" s="22" t="n">
+        <v>182.686</v>
+      </c>
+      <c r="K163" s="22" t="n">
+        <v>908.154</v>
+      </c>
+      <c r="M163" s="22" t="n">
+        <v>785.13</v>
+      </c>
+      <c r="R163" s="22" t="n">
+        <v>184.691</v>
+      </c>
+      <c r="S163" s="22" t="n">
+        <v>4230.011</v>
+      </c>
+      <c r="T163" s="22" t="n">
+        <v>3480.092</v>
+      </c>
+      <c r="U163" s="22" t="n">
+        <v>-1269.455</v>
+      </c>
+      <c r="V163" s="22" t="n">
+        <v>-907.328</v>
+      </c>
+      <c r="W163" s="22" t="n">
+        <v>-1352.917</v>
+      </c>
+      <c r="X163" s="22" t="n">
+        <v>908.154</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="20" t="inlineStr">
+        <is>
           <t>합병에 따른 현금성자산 증가</t>
         </is>
       </c>
-      <c r="S158" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T158" s="22" t="n">
+      <c r="S164" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" s="22" t="n">
         <v>1.81</v>
       </c>
-      <c r="U158" s="22" t="n">
+      <c r="U164" s="22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -8938,7 +9321,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="45" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>재무비율은 기말 잔액 기준 · 분기 손익은 최근 4분기 합산(TTM)</t>
         </is>
@@ -10272,7 +10655,7 @@
       <c r="L42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="46" t="inlineStr">
+      <c r="A43" s="47" t="inlineStr">
         <is>
           <t>부채비율</t>
         </is>
@@ -10324,7 +10707,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="46" t="inlineStr">
+      <c r="A44" s="47" t="inlineStr">
         <is>
           <t>순차입금비율</t>
         </is>
@@ -10376,7 +10759,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="46" t="inlineStr">
+      <c r="A45" s="47" t="inlineStr">
         <is>
           <t>자기자본비율</t>
         </is>
@@ -10428,7 +10811,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="46" t="inlineStr">
+      <c r="A46" s="47" t="inlineStr">
         <is>
           <t>유동비율</t>
         </is>
@@ -10480,7 +10863,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="46" t="inlineStr">
+      <c r="A47" s="47" t="inlineStr">
         <is>
           <t>당좌비율</t>
         </is>
@@ -10532,7 +10915,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="46" t="inlineStr">
+      <c r="A48" s="47" t="inlineStr">
         <is>
           <t>이자보상배율</t>
         </is>
@@ -10584,7 +10967,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="46" t="inlineStr">
+      <c r="A49" s="47" t="inlineStr">
         <is>
           <t>차입금 상환연수</t>
         </is>
@@ -10594,43 +10977,43 @@
           <t>4년↓ (버핏)</t>
         </is>
       </c>
-      <c r="C49" s="47">
+      <c r="C49" s="48">
         <f>IFERROR(IF((IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))&lt;=0,"적자",C28/(IF(COUNT('연간'!G44:J44)&lt;4,"",SUM('연간'!G44:J44)))),"")</f>
         <v/>
       </c>
-      <c r="D49" s="48">
+      <c r="D49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))&lt;=0,"적자",D28/(IF(COUNT('연간'!H44:K44)&lt;4,"",SUM('연간'!H44:K44)))),"")</f>
         <v/>
       </c>
-      <c r="E49" s="48">
+      <c r="E49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))&lt;=0,"적자",E28/(IF(COUNT('연간'!I44:L44)&lt;4,"",SUM('연간'!I44:L44)))),"")</f>
         <v/>
       </c>
-      <c r="F49" s="48">
+      <c r="F49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))&lt;=0,"적자",F28/(IF(COUNT('연간'!J44:M44)&lt;4,"",SUM('연간'!J44:M44)))),"")</f>
         <v/>
       </c>
-      <c r="G49" s="48">
+      <c r="G49" s="49">
         <f>IFERROR(IF((IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))&lt;=0,"적자",G28/(IF(COUNT('연간'!K44:N44)&lt;4,"",SUM('연간'!K44:N44)))),"")</f>
         <v/>
       </c>
-      <c r="H49" s="47">
+      <c r="H49" s="48">
         <f>IFERROR(IF(('연간'!T44)&lt;=0,"적자",H28/('연간'!T44)),"")</f>
         <v/>
       </c>
-      <c r="I49" s="48">
+      <c r="I49" s="49">
         <f>IFERROR(IF(('연간'!U44)&lt;=0,"적자",I28/('연간'!U44)),"")</f>
         <v/>
       </c>
-      <c r="J49" s="48">
+      <c r="J49" s="49">
         <f>IFERROR(IF(('연간'!V44)&lt;=0,"적자",J28/('연간'!V44)),"")</f>
         <v/>
       </c>
-      <c r="K49" s="48">
+      <c r="K49" s="49">
         <f>IFERROR(IF(('연간'!W44)&lt;=0,"적자",K28/('연간'!W44)),"")</f>
         <v/>
       </c>
-      <c r="L49" s="48">
+      <c r="L49" s="49">
         <f>IFERROR(IF(('연간'!X44)&lt;=0,"적자",L28/('연간'!X44)),"")</f>
         <v/>
       </c>
@@ -10654,7 +11037,7 @@
       <c r="L50" s="25" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="46" t="inlineStr">
+      <c r="A51" s="47" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
@@ -10706,7 +11089,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="46" t="inlineStr">
+      <c r="A52" s="47" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
@@ -10758,7 +11141,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="46" t="inlineStr">
+      <c r="A53" s="47" t="inlineStr">
         <is>
           <t>ROIC</t>
         </is>
@@ -10810,7 +11193,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="46" t="inlineStr">
+      <c r="A54" s="47" t="inlineStr">
         <is>
           <t>매출총이익률 (GPM)</t>
         </is>
@@ -10862,7 +11245,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="46" t="inlineStr">
+      <c r="A55" s="47" t="inlineStr">
         <is>
           <t>영업이익률 (OPM)</t>
         </is>
@@ -10914,7 +11297,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="46" t="inlineStr">
+      <c r="A56" s="47" t="inlineStr">
         <is>
           <t>순이익률</t>
         </is>
@@ -10984,7 +11367,7 @@
       <c r="L57" s="25" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="46" t="inlineStr">
+      <c r="A58" s="47" t="inlineStr">
         <is>
           <t>총자산회전율</t>
         </is>
@@ -11036,7 +11419,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="46" t="inlineStr">
+      <c r="A59" s="47" t="inlineStr">
         <is>
           <t>매출채권회전일수</t>
         </is>
@@ -11046,49 +11429,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C59" s="49">
+      <c r="C59" s="50">
         <f>IFERROR(C8/(IF(COUNT('연간'!G4:J4)&lt;4,"",SUM('연간'!G4:J4)))*365,"")</f>
         <v/>
       </c>
-      <c r="D59" s="50">
+      <c r="D59" s="51">
         <f>IFERROR(D8/(IF(COUNT('연간'!H4:K4)&lt;4,"",SUM('연간'!H4:K4)))*365,"")</f>
         <v/>
       </c>
-      <c r="E59" s="50">
+      <c r="E59" s="51">
         <f>IFERROR(E8/(IF(COUNT('연간'!I4:L4)&lt;4,"",SUM('연간'!I4:L4)))*365,"")</f>
         <v/>
       </c>
-      <c r="F59" s="50">
+      <c r="F59" s="51">
         <f>IFERROR(F8/(IF(COUNT('연간'!J4:M4)&lt;4,"",SUM('연간'!J4:M4)))*365,"")</f>
         <v/>
       </c>
-      <c r="G59" s="50">
+      <c r="G59" s="51">
         <f>IFERROR(G8/(IF(COUNT('연간'!K4:N4)&lt;4,"",SUM('연간'!K4:N4)))*365,"")</f>
         <v/>
       </c>
-      <c r="H59" s="49">
+      <c r="H59" s="50">
         <f>IFERROR(H8/('연간'!T4)*365,"")</f>
         <v/>
       </c>
-      <c r="I59" s="50">
+      <c r="I59" s="51">
         <f>IFERROR(I8/('연간'!U4)*365,"")</f>
         <v/>
       </c>
-      <c r="J59" s="50">
+      <c r="J59" s="51">
         <f>IFERROR(J8/('연간'!V4)*365,"")</f>
         <v/>
       </c>
-      <c r="K59" s="50">
+      <c r="K59" s="51">
         <f>IFERROR(K8/('연간'!W4)*365,"")</f>
         <v/>
       </c>
-      <c r="L59" s="50">
+      <c r="L59" s="51">
         <f>IFERROR(L8/('연간'!X4)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="46" t="inlineStr">
+      <c r="A60" s="47" t="inlineStr">
         <is>
           <t>재고자산회전일수</t>
         </is>
@@ -11098,49 +11481,49 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C60" s="49">
+      <c r="C60" s="50">
         <f>IFERROR(C9/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D60" s="50">
+      <c r="D60" s="51">
         <f>IFERROR(D9/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E60" s="50">
+      <c r="E60" s="51">
         <f>IFERROR(E9/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F60" s="50">
+      <c r="F60" s="51">
         <f>IFERROR(F9/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G60" s="50">
+      <c r="G60" s="51">
         <f>IFERROR(G9/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H60" s="49">
+      <c r="H60" s="50">
         <f>IFERROR(H9/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I60" s="50">
+      <c r="I60" s="51">
         <f>IFERROR(I9/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J60" s="50">
+      <c r="J60" s="51">
         <f>IFERROR(J9/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K60" s="50">
+      <c r="K60" s="51">
         <f>IFERROR(K9/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L60" s="50">
+      <c r="L60" s="51">
         <f>IFERROR(L9/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="46" t="inlineStr">
+      <c r="A61" s="47" t="inlineStr">
         <is>
           <t>매입채무회전일수</t>
         </is>
@@ -11150,49 +11533,49 @@
           <t>길수록 유리</t>
         </is>
       </c>
-      <c r="C61" s="49">
+      <c r="C61" s="50">
         <f>IFERROR(C19/(IF(COUNT('연간'!G11:J11)&lt;4,"",SUM('연간'!G11:J11)))*365,"")</f>
         <v/>
       </c>
-      <c r="D61" s="50">
+      <c r="D61" s="51">
         <f>IFERROR(D19/(IF(COUNT('연간'!H11:K11)&lt;4,"",SUM('연간'!H11:K11)))*365,"")</f>
         <v/>
       </c>
-      <c r="E61" s="50">
+      <c r="E61" s="51">
         <f>IFERROR(E19/(IF(COUNT('연간'!I11:L11)&lt;4,"",SUM('연간'!I11:L11)))*365,"")</f>
         <v/>
       </c>
-      <c r="F61" s="50">
+      <c r="F61" s="51">
         <f>IFERROR(F19/(IF(COUNT('연간'!J11:M11)&lt;4,"",SUM('연간'!J11:M11)))*365,"")</f>
         <v/>
       </c>
-      <c r="G61" s="50">
+      <c r="G61" s="51">
         <f>IFERROR(G19/(IF(COUNT('연간'!K11:N11)&lt;4,"",SUM('연간'!K11:N11)))*365,"")</f>
         <v/>
       </c>
-      <c r="H61" s="49">
+      <c r="H61" s="50">
         <f>IFERROR(H19/('연간'!T11)*365,"")</f>
         <v/>
       </c>
-      <c r="I61" s="50">
+      <c r="I61" s="51">
         <f>IFERROR(I19/('연간'!U11)*365,"")</f>
         <v/>
       </c>
-      <c r="J61" s="50">
+      <c r="J61" s="51">
         <f>IFERROR(J19/('연간'!V11)*365,"")</f>
         <v/>
       </c>
-      <c r="K61" s="50">
+      <c r="K61" s="51">
         <f>IFERROR(K19/('연간'!W11)*365,"")</f>
         <v/>
       </c>
-      <c r="L61" s="50">
+      <c r="L61" s="51">
         <f>IFERROR(L19/('연간'!X11)*365,"")</f>
         <v/>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="46" t="inlineStr">
+      <c r="A62" s="47" t="inlineStr">
         <is>
           <t>현금전환주기 (CCC)</t>
         </is>
@@ -11202,43 +11585,43 @@
           <t>짧을수록↑</t>
         </is>
       </c>
-      <c r="C62" s="49">
+      <c r="C62" s="50">
         <f>IF(OR(C59="",C60="",C61=""),"",IFERROR(C59+C60-C61,""))</f>
         <v/>
       </c>
-      <c r="D62" s="50">
+      <c r="D62" s="51">
         <f>IF(OR(D59="",D60="",D61=""),"",IFERROR(D59+D60-D61,""))</f>
         <v/>
       </c>
-      <c r="E62" s="50">
+      <c r="E62" s="51">
         <f>IF(OR(E59="",E60="",E61=""),"",IFERROR(E59+E60-E61,""))</f>
         <v/>
       </c>
-      <c r="F62" s="50">
+      <c r="F62" s="51">
         <f>IF(OR(F59="",F60="",F61=""),"",IFERROR(F59+F60-F61,""))</f>
         <v/>
       </c>
-      <c r="G62" s="50">
+      <c r="G62" s="51">
         <f>IF(OR(G59="",G60="",G61=""),"",IFERROR(G59+G60-G61,""))</f>
         <v/>
       </c>
-      <c r="H62" s="49">
+      <c r="H62" s="50">
         <f>IF(OR(H59="",H60="",H61=""),"",IFERROR(H59+H60-H61,""))</f>
         <v/>
       </c>
-      <c r="I62" s="50">
+      <c r="I62" s="51">
         <f>IF(OR(I59="",I60="",I61=""),"",IFERROR(I59+I60-I61,""))</f>
         <v/>
       </c>
-      <c r="J62" s="50">
+      <c r="J62" s="51">
         <f>IF(OR(J59="",J60="",J61=""),"",IFERROR(J59+J60-J61,""))</f>
         <v/>
       </c>
-      <c r="K62" s="50">
+      <c r="K62" s="51">
         <f>IF(OR(K59="",K60="",K61=""),"",IFERROR(K59+K60-K61,""))</f>
         <v/>
       </c>
-      <c r="L62" s="50">
+      <c r="L62" s="51">
         <f>IF(OR(L59="",L60="",L61=""),"",IFERROR(L59+L60-L61,""))</f>
         <v/>
       </c>
@@ -11262,7 +11645,7 @@
       <c r="L63" s="25" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="46" t="inlineStr">
+      <c r="A64" s="47" t="inlineStr">
         <is>
           <t>영업현금흐름 / 순이익</t>
         </is>
@@ -11314,7 +11697,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="46" t="inlineStr">
+      <c r="A65" s="47" t="inlineStr">
         <is>
           <t>FCF 마진</t>
         </is>
@@ -11366,7 +11749,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="46" t="inlineStr">
+      <c r="A66" s="47" t="inlineStr">
         <is>
           <t>CAPEX / 매출</t>
         </is>
@@ -11418,7 +11801,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="46" t="inlineStr">
+      <c r="A67" s="47" t="inlineStr">
         <is>
           <t>배당성향</t>
         </is>
@@ -13293,24 +13676,24 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="52" t="inlineStr">
         <is>
           <t>출처 · 쓴 결산단신</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="52" t="inlineStr">
+      <c r="A3" s="53" t="inlineStr">
         <is>
           <t>공시일</t>
         </is>
       </c>
-      <c r="B3" s="52" t="inlineStr">
+      <c r="B3" s="53" t="inlineStr">
         <is>
           <t>문서</t>
         </is>
       </c>
-      <c r="C3" s="52" t="inlineStr">
+      <c r="C3" s="53" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
